--- a/auto OMS Python/engines/shopee/sales_chihuy1984.xlsx
+++ b/auto OMS Python/engines/shopee/sales_chihuy1984.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="881">
   <si>
     <t>et_title_product_id</t>
   </si>
@@ -106,22 +106,37 @@
     <t>Combo Dao Rọc Giấy Thế Hệ Mới + 10 Lưỡi Dao SK5 Rọc giấy ,Thùng Carton Nhanh Chóng K138</t>
   </si>
   <si>
+    <t>435545534132</t>
+  </si>
+  <si>
+    <t>1 Dao + 30 lưỡi K138</t>
+  </si>
+  <si>
+    <t>DAO_ROCGIAY</t>
+  </si>
+  <si>
+    <t>1_dao_30_luoi_k138</t>
+  </si>
+  <si>
+    <t>109000</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
     <t>435545534130</t>
   </si>
   <si>
     <t>1 Dao + 10 lưỡi K138</t>
   </si>
   <si>
-    <t>DAO_ROCGIAY</t>
-  </si>
-  <si>
     <t>1_dao_10_luoi_k138</t>
   </si>
   <si>
     <t>69000</t>
   </si>
   <si>
-    <t>142</t>
+    <t>141</t>
   </si>
   <si>
     <t>435545534131</t>
@@ -136,22 +151,7 @@
     <t>89000</t>
   </si>
   <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>435545534132</t>
-  </si>
-  <si>
-    <t>1 Dao + 30 lưỡi K138</t>
-  </si>
-  <si>
-    <t>1_dao_30_luoi_k138</t>
-  </si>
-  <si>
-    <t>109000</t>
-  </si>
-  <si>
-    <t>47</t>
+    <t>70</t>
   </si>
   <si>
     <t>5176562851</t>
@@ -241,6 +241,18 @@
     <t>Pin sạc BESTON 1.2V AA AAA, Sạc pin chính hãng BESTON K146</t>
   </si>
   <si>
+    <t>151265825283</t>
+  </si>
+  <si>
+    <t>2 pin AAA800mAh</t>
+  </si>
+  <si>
+    <t>PINSAC_2PIN800</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
     <t>151265825285</t>
   </si>
   <si>
@@ -280,18 +292,6 @@
     <t>120000</t>
   </si>
   <si>
-    <t>151265825283</t>
-  </si>
-  <si>
-    <t>2 pin AAA800mAh</t>
-  </si>
-  <si>
-    <t>PINSAC_2PIN800</t>
-  </si>
-  <si>
-    <t>50000</t>
-  </si>
-  <si>
     <t>13279019429</t>
   </si>
   <si>
@@ -334,75 +334,75 @@
     <t>Set 10 Miếng Dán Ma Thuật Keo Nano Giúp Gọn Gàng Dây Điện Các Thiết Bị Điện Trong Nhà K55</t>
   </si>
   <si>
+    <t>385675684285</t>
+  </si>
+  <si>
+    <t>10 miếng trắng K55</t>
+  </si>
+  <si>
+    <t>MOCQUANAO_9LOK137</t>
+  </si>
+  <si>
+    <t>10_mieng_mau_trangK55</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>385675684286</t>
   </si>
   <si>
     <t>10 miếng đen K55</t>
   </si>
   <si>
-    <t>MOCQUANAO_9LOK137</t>
-  </si>
-  <si>
     <t>10_mieng_mau_denK55</t>
   </si>
   <si>
     <t>178</t>
   </si>
   <si>
-    <t>385675684285</t>
-  </si>
-  <si>
-    <t>10 miếng trắng K55</t>
-  </si>
-  <si>
-    <t>10_mieng_mau_trangK55</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>3356100732</t>
   </si>
   <si>
     <t>Tấm Phủ Lò Vi Sóng K150 – Chống Thấm, Chống Bụi, Chất Liệu PE Cao Cấp</t>
   </si>
   <si>
+    <t>155692751502</t>
+  </si>
+  <si>
+    <t>Hình Con Mèo,35cm x 85cm</t>
+  </si>
+  <si>
+    <t>BOC_LOVISONG</t>
+  </si>
+  <si>
+    <t>BOCLOVISONG_MEO</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>183265057646</t>
+  </si>
+  <si>
+    <t>Hình Hải Mã,35cm x 85cm</t>
+  </si>
+  <si>
+    <t>BOCLOVISONG_HAIMA</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>430662377056</t>
   </si>
   <si>
     <t>Hình Đại Dương,35cm x 85cm</t>
   </si>
   <si>
-    <t>BOC_LOVISONG</t>
-  </si>
-  <si>
     <t>BOCLOVISONG_DAIDUONG</t>
   </si>
   <si>
-    <t>155692751502</t>
-  </si>
-  <si>
-    <t>Hình Con Mèo,35cm x 85cm</t>
-  </si>
-  <si>
-    <t>BOCLOVISONG_MEO</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>183265057646</t>
-  </si>
-  <si>
-    <t>Hình Hải Mã,35cm x 85cm</t>
-  </si>
-  <si>
-    <t>BOCLOVISONG_HAIMA</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>10688144081</t>
   </si>
   <si>
@@ -436,7 +436,7 @@
     <t>79000</t>
   </si>
   <si>
-    <t>338</t>
+    <t>337</t>
   </si>
   <si>
     <t>28083598775</t>
@@ -445,6 +445,21 @@
     <t>COMBO 50 BỘ Tắc Kê Sắt + Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
   </si>
   <si>
+    <t>237690435218</t>
+  </si>
+  <si>
+    <t>50Bộ 6mmx32mm+ Vít</t>
+  </si>
+  <si>
+    <t>233417_combo_50_bo_tac_ke_vit_6mmx_32mm</t>
+  </si>
+  <si>
+    <t>115000</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
     <t>237690435219</t>
   </si>
   <si>
@@ -457,1722 +472,1707 @@
     <t>250000</t>
   </si>
   <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>237690435217</t>
+  </si>
+  <si>
+    <t>50Bộ 5mmx30mm+ Vít</t>
+  </si>
+  <si>
+    <t>233416_combo_50_bo_tac_ke_vit_5mmx_30mm</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>14815890188</t>
+  </si>
+  <si>
+    <t>Kẹp Cố Định Dây Điện, Cáp Mạng K114 – Keo Nano Siêu Dính, Không Cần Khoan</t>
+  </si>
+  <si>
+    <t>128008525451</t>
+  </si>
+  <si>
+    <t>10 Kẹp Đen 16mm</t>
+  </si>
+  <si>
+    <t>10 KẸP SIZE 16MM ĐEN K114</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>128008525452</t>
+  </si>
+  <si>
+    <t>10 Kẹp Đen 22mm</t>
+  </si>
+  <si>
+    <t>10 KẸP SIZE 22MM K114 ĐEN</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>128008525447</t>
+  </si>
+  <si>
+    <t>10 Kẹp Trắng 12mm</t>
+  </si>
+  <si>
+    <t>10 KẸP SIZE 12MM TRẮNG K114</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>128008525448</t>
+  </si>
+  <si>
+    <t>10 Kẹp Trắng 16mm</t>
+  </si>
+  <si>
+    <t>10 KẸP SIZE 16MM TRẮNG K114</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>128008525449</t>
+  </si>
+  <si>
+    <t>10 Kẹp Trắng 22mm</t>
+  </si>
+  <si>
+    <t>10 KẸP SIZE 22MM K114 TRẮNG</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>128008525450</t>
+  </si>
+  <si>
+    <t>10 Kẹp Đen 12mm</t>
+  </si>
+  <si>
+    <t>10 KẸP SIZE 12MM ĐEN K114</t>
+  </si>
+  <si>
+    <t>12455764340</t>
+  </si>
+  <si>
+    <t>Găng Tay Cách Nhiệt Silicon K09 – Dùng Nhà Bếp, Chống Nóng, Chống Trượt</t>
+  </si>
+  <si>
+    <t>104174135569</t>
+  </si>
+  <si>
+    <t>Giao Ngẫu Nhiên</t>
+  </si>
+  <si>
+    <t>GANGTAYCACHNHIET_K09</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>24418368117</t>
+  </si>
+  <si>
+    <t>Biến Tất Cả Quạt Thường Thành Quạt Sử Dụng Remote Với Bộ Mạch Điều Khiển Từ Xa Hàng Loại 1 K242</t>
+  </si>
+  <si>
+    <t>410305224432</t>
+  </si>
+  <si>
+    <t>1 Bộ Mạch + Remote</t>
+  </si>
+  <si>
+    <t>MẠCH QUẠT K242</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>168175352927</t>
+  </si>
+  <si>
+    <t>1 Bộ Mạch+Remote+PIN</t>
+  </si>
+  <si>
+    <t>bomachquatK242_PIN3A</t>
+  </si>
+  <si>
+    <t>260516445799</t>
+  </si>
+  <si>
+    <t>Mạch Mini +Remote</t>
+  </si>
+  <si>
+    <t>1bo_mach_remote_mini K102</t>
+  </si>
+  <si>
+    <t>15515891479</t>
+  </si>
+  <si>
+    <t>Nẹp Dây Điện Dán Tường Keo Nano Siêu Dính Thế Hệ Mới , Kẹp Dây Điện Cố Định an toàn tiện lợi dễ lắp đặt K110</t>
+  </si>
+  <si>
+    <t>203264569655</t>
+  </si>
+  <si>
+    <t>20 Nẹp Trong Đục Nhỏ</t>
+  </si>
+  <si>
+    <t>BO20MAUTRONGDUCNEW-K110</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>203264569652</t>
+  </si>
+  <si>
+    <t>16 Nẹp Trong Đục Lớn</t>
+  </si>
+  <si>
+    <t>BO16TRONGDUCNEW-K110</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>7690673333</t>
+  </si>
+  <si>
+    <t>Miếng Chặn Rác Silicone K20 – Ngăn Tắc Bồn Rửa, Đường Cống, Chống Tóc Rơi Xuống</t>
+  </si>
+  <si>
+    <t>82472964391</t>
+  </si>
+  <si>
+    <t>MIENGSILICON_BVCONGK20</t>
+  </si>
+  <si>
+    <t>2805379102</t>
+  </si>
+  <si>
+    <t>Bột/Thuốc Diệt Gián Sinh Học - Hiệu Quả Cực Mạnh, An Toàn Cho Gia Đình</t>
+  </si>
+  <si>
+    <t>257793964780</t>
+  </si>
+  <si>
+    <t>5BỊCH DIỆT GIÁN SALE</t>
+  </si>
+  <si>
+    <t>162612_combo_5_bich_diet_gian</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>147</t>
+  </si>
+  <si>
+    <t>31210759601</t>
+  </si>
+  <si>
+    <t>1 Bịch Diệt gián</t>
+  </si>
+  <si>
+    <t>1 BỊCH DIỆT GIÁN K154</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>737</t>
+  </si>
+  <si>
+    <t>195866698283</t>
+  </si>
+  <si>
+    <t>3 Bịch Diệt gián</t>
+  </si>
+  <si>
+    <t>162613_combo_3_bich_diet_gian</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>5381318046</t>
+  </si>
+  <si>
+    <t>Găng Tay Chống Nóng Lò Nướng K018 – Dày Dặn, Cách Nhiệt Tốt, An Toàn Khi Làm Bán</t>
+  </si>
+  <si>
+    <t>34051322550</t>
+  </si>
+  <si>
+    <t>GANGTAY_LAMBANHK18</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>2907252325</t>
+  </si>
+  <si>
+    <t>Đui Đèn Thông Minh E27 Điều Khiển Từ Xa, 5 Mức Hẹn Giờ Tắt, Kèm Remote + Pin, Không Cần Cài Đặt K84</t>
+  </si>
+  <si>
+    <t>290174216058</t>
+  </si>
+  <si>
+    <t>1 ĐUI ĐÈN DK K84</t>
+  </si>
+  <si>
+    <t>MOCDAN_TRONGSUOTK84</t>
+  </si>
+  <si>
+    <t>1_dui_den_dk_k84</t>
+  </si>
+  <si>
+    <t>3356099336</t>
+  </si>
+  <si>
+    <t>COMBO 3 Móc dán tường Cao Cấp kẹp giữ cây lau nhà , móc treo chổi chịu lực 6kg - K48</t>
+  </si>
+  <si>
+    <t>271839669458</t>
+  </si>
+  <si>
+    <t>COMBO 3 MÓC</t>
+  </si>
+  <si>
+    <t>K48</t>
+  </si>
+  <si>
+    <t>400347_combo_3_moc</t>
+  </si>
+  <si>
+    <t>29000</t>
+  </si>
+  <si>
+    <t>7456001637</t>
+  </si>
+  <si>
+    <t>Áo Trùm Máy Giặt Cao Cấp Chống Thấm Nước ,chống Bám Bụi Mẫu Mã Đa Dạng Đẹp Và Sang Trọng Lắp Đặt Dễ Dàng K142</t>
+  </si>
+  <si>
+    <t>108909146880</t>
+  </si>
+  <si>
+    <t>Cửangang ĐD 65X67X87</t>
+  </si>
+  <si>
+    <t>65X67X87NGANGDAIDUONG</t>
+  </si>
+  <si>
+    <t>110000</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>164368356467</t>
+  </si>
+  <si>
+    <t>CửaTrênMèo 65x65x105</t>
+  </si>
+  <si>
+    <t>CUATRENMEO65X65X105</t>
+  </si>
+  <si>
+    <t>48633594528</t>
+  </si>
+  <si>
+    <t>CửangangMèo 65x67x87</t>
+  </si>
+  <si>
+    <t>65X67X87NGANGMEO</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>164368356462</t>
+  </si>
+  <si>
+    <t>Cửa Trên 5KG Mèo</t>
+  </si>
+  <si>
+    <t>CUATREN5KGMEO</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>108909146891</t>
+  </si>
+  <si>
+    <t>Cửa trên 7KG DDương</t>
+  </si>
+  <si>
+    <t>TREN7KGDAIDUONG</t>
+  </si>
+  <si>
+    <t>38634334554</t>
+  </si>
+  <si>
+    <t>Cửa ngang 7KG Mèo</t>
+  </si>
+  <si>
+    <t>CUANGANG7KGMEO</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>108909146879</t>
+  </si>
+  <si>
+    <t>Cửa Trên 5KG ĐDương</t>
+  </si>
+  <si>
+    <t>TREN5KGDAIDUONG</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>108909146889</t>
+  </si>
+  <si>
+    <t>CỬATRÊNDD 65X65X105</t>
+  </si>
+  <si>
+    <t>TREN65X65X105DAIDUONG</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>108909146882</t>
+  </si>
+  <si>
+    <t>Cửa ngang 7KG ĐDương</t>
+  </si>
+  <si>
+    <t>CUANGANG7KGDAIDUONG</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>38634334556</t>
+  </si>
+  <si>
+    <t>Cửa trên 7KG Mèo</t>
+  </si>
+  <si>
+    <t>CUATREN7KGMEO</t>
+  </si>
+  <si>
+    <t>4548364452</t>
+  </si>
+  <si>
+    <t>COMBO 12 KẸP DÁN CỐ ĐỊNH DÂY CÁP SẠC,DÂY ĐIỆN GIÚP LÀM GỌN GÀNG DÂY ĐIỆN K72</t>
+  </si>
+  <si>
+    <t>249164749143</t>
+  </si>
+  <si>
+    <t>COMBO 12 KẸP ĐENK72</t>
+  </si>
+  <si>
+    <t>526675_combo_12_kep_denk72</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>249164749142</t>
+  </si>
+  <si>
+    <t>COMBO 1 KẸP TRẮNGK72</t>
+  </si>
+  <si>
+    <t>526675_combo_1_kep_trangk72</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>4848363969</t>
+  </si>
+  <si>
+    <t>Miếng Dán Gắn Ổ Cắm, Thiết Bị Điện – Siêu Dính, Dễ Tháo Lắp K059</t>
+  </si>
+  <si>
+    <t>64453593966</t>
+  </si>
+  <si>
+    <t>Màu Xám</t>
+  </si>
+  <si>
+    <t>ChihuyT069</t>
+  </si>
+  <si>
+    <t>K059_THANHTRUOTXAM</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>64453593967</t>
+  </si>
+  <si>
+    <t>Màu Trắng</t>
+  </si>
+  <si>
+    <t>K059_THANHTRUOTTRANG</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>5451944240</t>
+  </si>
+  <si>
+    <t>Thuốc diệt gián Nội Địa Hiểu Qủa Nhanh Chóng Trọng Lượng 1 Gói 5g K154</t>
+  </si>
+  <si>
+    <t>168754313020</t>
+  </si>
+  <si>
+    <t>dietgian</t>
+  </si>
+  <si>
+    <t>185866720568</t>
+  </si>
+  <si>
+    <t>71037223628</t>
+  </si>
+  <si>
+    <t>1Bịch Diệt gián</t>
+  </si>
+  <si>
+    <t>14008640325</t>
+  </si>
+  <si>
+    <t>Cọ Vệ Sinh Khe Cửa Sổ 2 Trong 1 K012 – Đa Năng, Làm Sạch Mọi Ngóc Ngách</t>
+  </si>
+  <si>
+    <t>37911997623</t>
+  </si>
+  <si>
+    <t>COLAMSACH_K12</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>11135551865</t>
+  </si>
+  <si>
+    <t>Mũ Gội Đầu Cho Bé K62 – Chống Nước Vào Mắt, Êm Đầu, Xốp Mềm Co Giãn</t>
+  </si>
+  <si>
+    <t>300123893866</t>
+  </si>
+  <si>
+    <t>Màu Hồng</t>
+  </si>
+  <si>
+    <t>MUGOIDAU_DETHUONGK62</t>
+  </si>
+  <si>
+    <t>mau_hong K62</t>
+  </si>
+  <si>
+    <t>300123893865</t>
+  </si>
+  <si>
+    <t>Màu Vàng</t>
+  </si>
+  <si>
+    <t>mau_vang K62</t>
+  </si>
+  <si>
+    <t>24768421006</t>
+  </si>
+  <si>
+    <t>COMBO 20 Tắc Kê Sắt + 20 Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
+  </si>
+  <si>
+    <t>415230669086</t>
+  </si>
+  <si>
+    <t>20 Bộ KT 6mm X 32mm</t>
+  </si>
+  <si>
+    <t>BO20TACKE6X32MMK243</t>
+  </si>
+  <si>
+    <t>85000</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>415230669087</t>
+  </si>
+  <si>
+    <t>20 Bộ KT 8mm X 60mm</t>
+  </si>
+  <si>
+    <t>20BOKT 8mmX60mm K243</t>
+  </si>
+  <si>
+    <t>135000</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>415230669085</t>
+  </si>
+  <si>
+    <t>20 Bộ KT 5mm X 30mm</t>
+  </si>
+  <si>
+    <t>20BOTACKE5X30MMK243</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>5948362499</t>
+  </si>
+  <si>
+    <t>[Bộ 20/16] Nẹp Dây Điện Dán Tường Trong Suốt - Kẹp Cố Định Dây Điện/Cáp Mạng Thông Minh, Giữ Nhà Cửa Gọn Gàng K145</t>
+  </si>
+  <si>
+    <t>249134430410</t>
+  </si>
+  <si>
+    <t>20 Nẹp Trong Đục NEW</t>
+  </si>
+  <si>
+    <t>BO20TRONGDUCK110</t>
+  </si>
+  <si>
+    <t>249134430411</t>
+  </si>
+  <si>
+    <t>16 Nẹp Trong Đục NEW</t>
+  </si>
+  <si>
+    <t>BO16TRONGDUCK110</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>249134430408</t>
+  </si>
+  <si>
+    <t>Bộ 20 Nẹp Nhỏ + Keo</t>
+  </si>
+  <si>
+    <t>BO20TRONGSUOT</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>249134430409</t>
+  </si>
+  <si>
+    <t>Bộ 16 Nẹp Lớn + Keo</t>
+  </si>
+  <si>
+    <t>BO16TRONGSUOT</t>
+  </si>
+  <si>
+    <t>6064773742</t>
+  </si>
+  <si>
+    <t>Màng Lọc Dầu Mỡ Máy Hút Mùi K153 – Giữ Bếp Sạch, Chống Bám Bẩn Hiệu Quả</t>
+  </si>
+  <si>
+    <t>41950199165</t>
+  </si>
+  <si>
+    <t>MANGLOC_CHANDAUMO</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>8882127653</t>
+  </si>
+  <si>
+    <t>Cuộn 17 Túi Rác Tự Hủy Sinh Học K101 – Mỏng, Bền, Thân Thiện Môi Trường</t>
+  </si>
+  <si>
+    <t>101149234142</t>
+  </si>
+  <si>
+    <t>TUIRAC_TUHUYK101</t>
+  </si>
+  <si>
+    <t>13615381825</t>
+  </si>
+  <si>
+    <t>Bộ 100 Đinh 2 Đầu Dùng Để Đóng Chân Tường ,Tủ Kệ Bếp Che Khuyết Điểm K97</t>
+  </si>
+  <si>
+    <t>127878289683</t>
+  </si>
+  <si>
+    <t>Bộ 100 Đinh + ống</t>
+  </si>
+  <si>
+    <t>K97_100DINH2DAU</t>
+  </si>
+  <si>
+    <t>6856001620</t>
+  </si>
+  <si>
+    <t>Bọc Tủ Lạnh K144 – Chống Nước, Chống Bụi, Có Túi 2 Bên Tiện Lợi</t>
+  </si>
+  <si>
+    <t>300002545460</t>
+  </si>
+  <si>
+    <t>Hình Đại Dương,130cm x 55cm</t>
+  </si>
+  <si>
+    <t>BOC_TULANH</t>
+  </si>
+  <si>
+    <t>249692_hinh_dai_duong_130cm_x_55cm</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>164360512854</t>
+  </si>
+  <si>
+    <t>Hình Con Mèo,130cm x 55cm</t>
+  </si>
+  <si>
+    <t>BOCTULANH_MEO</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>164360512855</t>
+  </si>
+  <si>
+    <t>Hình Con Thỏ,130cm x 55cm</t>
+  </si>
+  <si>
+    <t>BOCTULANH_THO</t>
+  </si>
+  <si>
+    <t>7037990835</t>
+  </si>
+  <si>
+    <t>Combo 5 Chốt Cửa Tủ inox dày 0.8mm (Roller Catch) - Lắp Đặt Nhanh, Đóng Êm Ái K023</t>
+  </si>
+  <si>
+    <t>330078341967</t>
+  </si>
+  <si>
+    <t>COMBO 5 CHỐT 7 MÀU</t>
+  </si>
+  <si>
+    <t>combo_5_chot_7_mau</t>
+  </si>
+  <si>
+    <t>249019174211</t>
+  </si>
+  <si>
+    <t>COMBO 5 CHỐT BẠC</t>
+  </si>
+  <si>
+    <t>combo_5_chot_bac</t>
+  </si>
+  <si>
     <t>83</t>
   </si>
   <si>
-    <t>237690435217</t>
-  </si>
-  <si>
-    <t>50Bộ 5mmx30mm+ Vít</t>
-  </si>
-  <si>
-    <t>233416_combo_50_bo_tac_ke_vit_5mmx_30mm</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>237690435218</t>
-  </si>
-  <si>
-    <t>50Bộ 6mmx32mm+ Vít</t>
-  </si>
-  <si>
-    <t>233417_combo_50_bo_tac_ke_vit_6mmx_32mm</t>
-  </si>
-  <si>
-    <t>115000</t>
-  </si>
-  <si>
-    <t>12455764340</t>
-  </si>
-  <si>
-    <t>Găng Tay Cách Nhiệt Silicon K09 – Dùng Nhà Bếp, Chống Nóng, Chống Trượt</t>
-  </si>
-  <si>
-    <t>104174135569</t>
-  </si>
-  <si>
-    <t>Giao Ngẫu Nhiên</t>
-  </si>
-  <si>
-    <t>GANGTAYCACHNHIET_K09</t>
-  </si>
-  <si>
-    <t>25000</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>14815890188</t>
-  </si>
-  <si>
-    <t>Kẹp Cố Định Dây Điện, Cáp Mạng K114 – Keo Nano Siêu Dính, Không Cần Khoan</t>
-  </si>
-  <si>
-    <t>128008525451</t>
-  </si>
-  <si>
-    <t>10 Kẹp Đen 16mm</t>
-  </si>
-  <si>
-    <t>10 KẸP SIZE 16MM ĐEN K114</t>
-  </si>
-  <si>
-    <t>40000</t>
-  </si>
-  <si>
-    <t>128008525452</t>
-  </si>
-  <si>
-    <t>10 Kẹp Đen 22mm</t>
-  </si>
-  <si>
-    <t>10 KẸP SIZE 22MM K114 ĐEN</t>
-  </si>
-  <si>
-    <t>45000</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>128008525447</t>
-  </si>
-  <si>
-    <t>10 Kẹp Trắng 12mm</t>
-  </si>
-  <si>
-    <t>10 KẸP SIZE 12MM TRẮNG K114</t>
-  </si>
-  <si>
-    <t>35000</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>128008525448</t>
-  </si>
-  <si>
-    <t>10 Kẹp Trắng 16mm</t>
-  </si>
-  <si>
-    <t>10 KẸP SIZE 16MM TRẮNG K114</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>128008525449</t>
-  </si>
-  <si>
-    <t>10 Kẹp Trắng 22mm</t>
-  </si>
-  <si>
-    <t>10 KẸP SIZE 22MM K114 TRẮNG</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>128008525450</t>
-  </si>
-  <si>
-    <t>10 Kẹp Đen 12mm</t>
-  </si>
-  <si>
-    <t>10 KẸP SIZE 12MM ĐEN K114</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>24418368117</t>
-  </si>
-  <si>
-    <t>Biến Tất Cả Quạt Thường Thành Quạt Sử Dụng Remote Với Bộ Mạch Điều Khiển Từ Xa Hàng Loại 1 K242</t>
-  </si>
-  <si>
-    <t>260516445799</t>
-  </si>
-  <si>
-    <t>Mạch Mini +Remote</t>
-  </si>
-  <si>
-    <t>1bo_mach_remote_mini K102</t>
-  </si>
-  <si>
-    <t>410305224432</t>
-  </si>
-  <si>
-    <t>1 Bộ Mạch + Remote</t>
-  </si>
-  <si>
-    <t>MẠCH QUẠT K242</t>
+    <t>7623356102</t>
+  </si>
+  <si>
+    <t>Bộ 10 Đôi Đũa Khắc Họa Tiết Hoa Anh Đào Chống Mốc Chống Trơn Trượt Độ Dài 24cm và 27cm - K054</t>
+  </si>
+  <si>
+    <t>176458351242</t>
+  </si>
+  <si>
+    <t>Đũa Hoa Anh Đào 24cm</t>
+  </si>
+  <si>
+    <t>duahopkim</t>
+  </si>
+  <si>
+    <t>K54HOAANHDAO24CM</t>
+  </si>
+  <si>
+    <t>65000</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>225208121707</t>
+  </si>
+  <si>
+    <t>Đũa Hoa Anh Đào 27cm</t>
+  </si>
+  <si>
+    <t>K54HOAANHDAO27CM</t>
+  </si>
+  <si>
+    <t>11135553238</t>
+  </si>
+  <si>
+    <t>Kệ Để Đồ Nhà Bếp &amp; Phòng Tắm Nhôm Không Rỉ – Chịu Lực 30kg – Dán Tường K108</t>
+  </si>
+  <si>
+    <t>207227212402</t>
+  </si>
+  <si>
+    <t>TAM GIÁC 3 LỚP ĐEN</t>
+  </si>
+  <si>
+    <t>THANHCHANCUA_MUTXOPK108</t>
+  </si>
+  <si>
+    <t>K108_TGMAUDEN</t>
+  </si>
+  <si>
+    <t>139000</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>207227212403</t>
+  </si>
+  <si>
+    <t>CHỮ NHẬT 2 LỚP BẠC</t>
+  </si>
+  <si>
+    <t>K108_CNMAUBAC</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>207227212404</t>
+  </si>
+  <si>
+    <t>TAM GIÁC 2 LỚP BẠC</t>
+  </si>
+  <si>
+    <t>K108_TGMAUBAC</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>168175352927</t>
-  </si>
-  <si>
-    <t>1 Bộ Mạch+Remote+PIN</t>
-  </si>
-  <si>
-    <t>bomachquatK242_PIN3A</t>
+    <t>207227212401</t>
+  </si>
+  <si>
+    <t>CHỮ NHẬT 3 LỚP ĐEN</t>
+  </si>
+  <si>
+    <t>K108_CNMAUDEN</t>
+  </si>
+  <si>
+    <t>7756001691</t>
+  </si>
+  <si>
+    <t>Tạp Dề, Yếm Nấu Ăn ,Học Vẽ Có Lót Tay, Chống Thấm Nước Loại Đẹp K07</t>
+  </si>
+  <si>
+    <t>155972301740</t>
+  </si>
+  <si>
+    <t>Màu Nâu Xanh</t>
+  </si>
+  <si>
+    <t>ChihuyT078</t>
+  </si>
+  <si>
+    <t>TAPDENAUXANHK07</t>
+  </si>
+  <si>
+    <t>164727386290</t>
+  </si>
+  <si>
+    <t>Size Nhí ( Xanh)</t>
+  </si>
+  <si>
+    <t>TAPDENHIXANHK07</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>164727386291</t>
+  </si>
+  <si>
+    <t>Size Nhí ( Vàng)</t>
+  </si>
+  <si>
+    <t>TAPDENHIVANGK07</t>
+  </si>
+  <si>
+    <t>155972301739</t>
+  </si>
+  <si>
+    <t>Màu Xanh Hồng</t>
+  </si>
+  <si>
+    <t>TAPDEXANHHONGK07</t>
+  </si>
+  <si>
+    <t>8690874835</t>
+  </si>
+  <si>
+    <t>Khăn Lau Đa Năng Microfiber K074 – Dày Dặn, Hút Nước Gấp 3 Lần</t>
+  </si>
+  <si>
+    <t>47065318525</t>
+  </si>
+  <si>
+    <t>KHANLAU_OTOK74</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>8788662942</t>
+  </si>
+  <si>
+    <t>Set 10 NẸP LÁ DÁN TƯỜNG – Giữ Dây Gọn Gàng, Dán Cây Cực Chắc, KHÔNG CẦN KHOAN!</t>
+  </si>
+  <si>
+    <t>275975546309</t>
+  </si>
+  <si>
+    <t>10 NẸP LÁ CÂY + KEO</t>
+  </si>
+  <si>
+    <t>MIENGDAN_PHANTANGK118</t>
+  </si>
+  <si>
+    <t>10_nep_hinh_la_cayK109</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>18767750537</t>
+  </si>
+  <si>
+    <t>Băng Dính Gai Làm Gọn Dây Điện, Băng Dán Gai Đa Năng Băng Nhám Làm Gọn Góc Pc, Dây Cáp Sạc, Tai Nghe K205</t>
+  </si>
+  <si>
+    <t>213491275436</t>
+  </si>
+  <si>
+    <t>1 Cuộn Dài 1,5M</t>
+  </si>
+  <si>
+    <t>BANGDINH_K205</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>9523434925</t>
+  </si>
+  <si>
+    <t>Dũa Móng Tay 6 Mặt K106 – Vừa Chà Nhám Vừa Đánh Bóng, Móng Mịn Như Spa</t>
+  </si>
+  <si>
+    <t>44051336796</t>
+  </si>
+  <si>
+    <t>DUAMONGTAY_6MATK106</t>
+  </si>
+  <si>
+    <t>10335548632</t>
+  </si>
+  <si>
+    <t>Túi Đựng Rác Tự Phân Hủy K70 – Có Dây Rút, Sạch Sẽ, Thân Thiện Môi Trường</t>
+  </si>
+  <si>
+    <t>84441035566</t>
+  </si>
+  <si>
+    <t>TUIRAC_DAYRUTK70</t>
+  </si>
+  <si>
+    <t>24478477879</t>
+  </si>
+  <si>
+    <t>Chai Xịt Vệ Sinh Dạng Bọt Tuyết Tẩy Rửa Nhà Bếp Siêu Đa Năng,Tẩy Sạch Vết Dầu Mỡ Cứng Đầu Global 500ml - K46</t>
+  </si>
+  <si>
+    <t>255766638889</t>
+  </si>
+  <si>
+    <t>1 chai 500ml</t>
+  </si>
+  <si>
+    <t>K46_CHAIXITVESINHBEP</t>
+  </si>
+  <si>
+    <t>119000</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>11076966036</t>
+  </si>
+  <si>
+    <t>Keo Chống Thấm Thế Hệ Mới GOSU Thời Gian Khô Nhanh Chóng Thích Hợp Quét Ngoài Trời ,Sân Thượng K162</t>
+  </si>
+  <si>
+    <t>242926384187</t>
+  </si>
+  <si>
+    <t>1 TÚI KEO 500ML K162</t>
+  </si>
+  <si>
+    <t>K162_KEOCHONGTHAM500ML</t>
+  </si>
+  <si>
+    <t>736</t>
+  </si>
+  <si>
+    <t>11708283596</t>
+  </si>
+  <si>
+    <t>100 Sợi Dây Rút Nhựa Dài 100mm và 200mm - K36</t>
+  </si>
+  <si>
+    <t>258985454595</t>
+  </si>
+  <si>
+    <t>100 Dây Dài 200mm</t>
+  </si>
+  <si>
+    <t>DAYRUT_K36</t>
+  </si>
+  <si>
+    <t>400348_100_day_dai_200mm</t>
+  </si>
+  <si>
+    <t>258985454594</t>
+  </si>
+  <si>
+    <t>100 Dây Dài 100mm</t>
+  </si>
+  <si>
+    <t>400348_100_day_dai_100mm</t>
+  </si>
+  <si>
+    <t>12015405187</t>
+  </si>
+  <si>
+    <t>Công Tắc Cảm Biến Ánh Sáng K263 Tự Động Bật Đèn Khi Trời Tối – Tắt Khi Trời Sáng Tiết Kiệm Điện Cho Ngoài Trời</t>
+  </si>
+  <si>
+    <t>128395394060</t>
+  </si>
+  <si>
+    <t>1 Bộ  AS10K263</t>
+  </si>
+  <si>
+    <t>MOCNHUA_TREOQUANAOK78</t>
+  </si>
+  <si>
+    <t>K263-AS10</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>12220381107</t>
+  </si>
+  <si>
+    <t>Bộ 10 miếng dán cố định thảm lót sàn ô tô - Chống trơn trượt, tái sử dụng nhiều lần K116</t>
+  </si>
+  <si>
+    <t>237531224352</t>
+  </si>
+  <si>
+    <t>COMBO 10MIẾNG 5X5CM</t>
+  </si>
+  <si>
+    <t>MIENGDANKEO_2MATK116</t>
+  </si>
+  <si>
+    <t>167477_combo_10mieng_5x5cm</t>
+  </si>
+  <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>13315378460</t>
+  </si>
+  <si>
+    <t>Cuộn Ron Cửa Chặn Khe Hở Ngăn Bụi,Nước,Côn Trùng, Cách Âm Chất Liệu TPE Cao Cấp K75</t>
+  </si>
+  <si>
+    <t>218229468770</t>
+  </si>
+  <si>
+    <t>5CM X 1M MÀU NÂU K75</t>
+  </si>
+  <si>
+    <t>CUONRON_CUACHONGONK75</t>
+  </si>
+  <si>
+    <t>K75_MAUNAU5CM1M</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>218229468768</t>
+  </si>
+  <si>
+    <t>5CMX1M MÀU TRẮNG K75</t>
+  </si>
+  <si>
+    <t>K75_MAUTRANG5CM1M</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>218229468769</t>
+  </si>
+  <si>
+    <t>5CM X 1M MÀU XÁM K75</t>
+  </si>
+  <si>
+    <t>K75_MAUXAM5CM1M</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>14108638821</t>
+  </si>
+  <si>
+    <t>Cây Cọ Rửa Ly Cốc Silicon K013 – Tạo Bọt, Không Trầy, Dùng Được Cho Bình Sữa</t>
+  </si>
+  <si>
+    <t>122624695768</t>
+  </si>
+  <si>
+    <t>màu ngẫu nhiên</t>
+  </si>
+  <si>
+    <t>CAYCOSILICON_K13</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>14109452622</t>
+  </si>
+  <si>
+    <t>Túi Vải Chia Ngăn Đựng Đồ Lót Tất Vớ K026 – Gấp Gọn, Dễ Tìm, Dễ Sắp Xếp</t>
+  </si>
+  <si>
+    <t>28257567996</t>
+  </si>
+  <si>
+    <t>Túi Vải 11 ngăn</t>
+  </si>
+  <si>
+    <t>TUIVAI11NGANK26</t>
+  </si>
+  <si>
+    <t>114195866554</t>
+  </si>
+  <si>
+    <t>Túi Vải 6 ngăn</t>
+  </si>
+  <si>
+    <t>TUIVAIDUNGDO_6NGANK26</t>
+  </si>
+  <si>
+    <t>114195866555</t>
+  </si>
+  <si>
+    <t>Túi Vải 7 ngăn</t>
+  </si>
+  <si>
+    <t>TUIVAIDUNGDO_7NGANK26</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>14677195925</t>
+  </si>
+  <si>
+    <t>Gioăng Bồn Cầu Ngăn Mùi Hôi, Ngăn Côn Trùng – Linh Kiện Cực Cần Khi Lắp Bồn Cầu K168</t>
+  </si>
+  <si>
+    <t>147762755036</t>
+  </si>
+  <si>
+    <t>1 Bộ Ống 100-110mm</t>
+  </si>
+  <si>
+    <t>BO100-110mmK168</t>
+  </si>
+  <si>
+    <t>239000</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>15477291455</t>
+  </si>
+  <si>
+    <t>Bàn Chải Lông Mềm, Không Làm Tổn Thương Quần Áo, Giày Dép,Vệ Sinh Đa Năng, Cọ Rửa Giày, Cọ Rửa Gia Dụng Cao Cấp K172</t>
+  </si>
+  <si>
+    <t>138299343386</t>
+  </si>
+  <si>
+    <t>Màu Xanh Dương K172</t>
+  </si>
+  <si>
+    <t>mau_xanh_duong_k172</t>
+  </si>
+  <si>
+    <t>138299343387</t>
+  </si>
+  <si>
+    <t>Màu Xám K172</t>
+  </si>
+  <si>
+    <t>mau_xam_k172</t>
+  </si>
+  <si>
+    <t>17595269902</t>
+  </si>
+  <si>
+    <t>Viên Thả Bồn Cầu 3IN1 Vừa Vệ Sinh ,Diệt Vi Khuẩn,Làm Bóng Men Sứ Bồn Cầu Vừa Tỏa Hương Thơm Mát Mẫu Mới K222</t>
+  </si>
+  <si>
+    <t>395510815656</t>
+  </si>
+  <si>
+    <t>COMBO 10 VIÊN 3IN1</t>
+  </si>
+  <si>
+    <t>COMBO10VIENK222</t>
+  </si>
+  <si>
+    <t>165000</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>395510815655</t>
+  </si>
+  <si>
+    <t>COMBO 5 VIÊN 3IN1</t>
+  </si>
+  <si>
+    <t>COMBO5VIEN3IN1K222</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>18314797680</t>
+  </si>
+  <si>
+    <t>Ron Chặn Khe Cửa Giảm Tiếng Ồn Chất Liệu TPE  – Thanh Chắn Khe Hở Chống Gió Lùa, Giữ Nhiệt Điều Hòa K185</t>
+  </si>
+  <si>
+    <t>265476202386</t>
+  </si>
+  <si>
+    <t>1Cuộn Nâu 3,5cm x 2M</t>
+  </si>
+  <si>
+    <t>NAU_3,5cmx2mK185</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>265476202387</t>
+  </si>
+  <si>
+    <t>1Cuộn Xám 3,5cm x 2M</t>
+  </si>
+  <si>
+    <t>XAM_3,5cmx2mK185</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>435548140512</t>
+  </si>
+  <si>
+    <t>1Cuộn Trắng 3,5cmx2M</t>
+  </si>
+  <si>
+    <t>TRANG_3,5cmx2mK185</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>435548140513</t>
+  </si>
+  <si>
+    <t>1Cuộn Nâu 5cm x 2M</t>
+  </si>
+  <si>
+    <t>NAU_5cmx2mK185</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>435548140514</t>
+  </si>
+  <si>
+    <t>1Cuộn Xám 5cm x 2M</t>
+  </si>
+  <si>
+    <t>XAM_5cmx2mK185</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>435548140515</t>
+  </si>
+  <si>
+    <t>1Cuộn Trắng 5cmx2M</t>
+  </si>
+  <si>
+    <t>TRANG_5cmx2mK185</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>19660248478</t>
+  </si>
+  <si>
+    <t>Thước Dây Cuộn Đo 3 Vòng Tự Động Chỉ Cần 1 Nút Bấm giúp Quản Lí Số Đo Cơ Thể Mỗi Ngày K204</t>
+  </si>
+  <si>
+    <t>203074115330</t>
+  </si>
+  <si>
+    <t>THUOCDAY_K204</t>
+  </si>
+  <si>
+    <t>27181536554</t>
+  </si>
+  <si>
+    <t>Mũi Khoan Lệch Tâm Đa Năng Chuyên Khoan Gạch Men Cứng, Gỗ, Tường, KimLoại All In One Khoan Nhanh Và Nhẹ K265</t>
+  </si>
+  <si>
+    <t>237603798079</t>
+  </si>
+  <si>
+    <t>COMBO 6-8-10-12MM</t>
+  </si>
+  <si>
+    <t>205706_combo_4_mui_6_8_10_12mm_k265</t>
+  </si>
+  <si>
+    <t>125000</t>
+  </si>
+  <si>
+    <t>237603798075</t>
+  </si>
+  <si>
+    <t>1 MŨI KHOAN 6MM K265</t>
+  </si>
+  <si>
+    <t>1_mui_khoan_6mm_k265</t>
+  </si>
+  <si>
+    <t>237603798076</t>
+  </si>
+  <si>
+    <t>1 MŨI KHOAN 8MM K265</t>
+  </si>
+  <si>
+    <t>1_mui_khoan_8mm_k265</t>
+  </si>
+  <si>
+    <t>33000</t>
+  </si>
+  <si>
+    <t>237603798077</t>
+  </si>
+  <si>
+    <t>1 MŨIKHOAN 10MM K265</t>
+  </si>
+  <si>
+    <t>1_muikhoan_10mm_k265</t>
+  </si>
+  <si>
+    <t>237603798078</t>
+  </si>
+  <si>
+    <t>1 MŨIKHOAN 12MM K265</t>
+  </si>
+  <si>
+    <t>1_muikhoan_12mm_k265</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>21428120893</t>
+  </si>
+  <si>
+    <t>Móc Inox Dán Tường Siêu Dính Treo Thau Chậu, Nồi ,Thớt , Khăn, Quần Áo/ Giá Gắn Tường Treo Đồ Nhà Bếp, Nhà Tắm K190</t>
+  </si>
+  <si>
+    <t>181456809001</t>
+  </si>
+  <si>
+    <t>MOCDANTUONGTREOTHAU_K190</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>22327610052</t>
+  </si>
+  <si>
+    <t>Dụng Cụ Đa Năng Mở Nắp Tất Cả Đồ Hộp Dễ Dàng Và Nhanh Chóng K210</t>
+  </si>
+  <si>
+    <t>146663161285</t>
+  </si>
+  <si>
+    <t>Màu Ngẫu Nhiên</t>
+  </si>
+  <si>
+    <t>DUNGCUMONAP_K210</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>25277881916</t>
+  </si>
+  <si>
+    <t>Đầu Nam Châm Gắn Mũi Bắt Vít Siêu Hít Chất Liệu Thép Hợp Kim S2 Siêu Bền giúp giữ chặt vít khi siết không sợ rớt K245</t>
+  </si>
+  <si>
+    <t>236290515417</t>
+  </si>
+  <si>
+    <t>1 Cái Đầu Nam Châm</t>
+  </si>
+  <si>
+    <t>K245_DAUNAMCHAMBATVIT</t>
+  </si>
+  <si>
+    <t>24428476358</t>
+  </si>
+  <si>
+    <t>Nước Giặt Đồ Lót Nano Bạc K252 – Khử Mùi, Kháng Khuẩn, Ngăn Viêm Nhiễm Hiệu Quả</t>
+  </si>
+  <si>
+    <t>147290375577</t>
+  </si>
+  <si>
+    <t>1 Chai 300ml</t>
+  </si>
+  <si>
+    <t>K252_NUOCGIATDOLOT</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>24559734917</t>
+  </si>
+  <si>
+    <t>Combo 5 Miếng thép sửa bản lề tủ, miếng sửa bản lề tủ, tấm thép sửa bản lề dễ dàng và tiết kiệm chi phí K237</t>
+  </si>
+  <si>
+    <t>320375059047</t>
+  </si>
+  <si>
+    <t>COMBO 5 MIẾNG K237</t>
+  </si>
+  <si>
+    <t>305410_5_mieng_hinh_vuong</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>25006646227</t>
+  </si>
+  <si>
+    <t>Dụng Cụ Bịt Kín Ống Thoát Nước Silicone – Chống Mùi, Chống Côn Trùng – Siêu Êm, Siêu Bền K258</t>
+  </si>
+  <si>
+    <t>440327644403</t>
+  </si>
+  <si>
+    <t>1 BỘ ỐNG 60-65MM</t>
+  </si>
+  <si>
+    <t>K258_60-65MM</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>440327644401</t>
+  </si>
+  <si>
+    <t>1 BỘ ỐNG 35-40MM</t>
+  </si>
+  <si>
+    <t>K258_35-40MM</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>440327644402</t>
+  </si>
+  <si>
+    <t>1 BỘ ỐNG 45-50MM</t>
+  </si>
+  <si>
+    <t>K258_45-50MM</t>
+  </si>
+  <si>
+    <t>25060391669</t>
+  </si>
+  <si>
+    <t>Gioăng Khử Mùi Hôi Bồn Cầu Cao Cấp, Ron Chống Hôi Bồn Cầu Dụng Cụ Không Thể Thiếu Khi Lắp Đặt Bồn Cầu K239</t>
+  </si>
+  <si>
+    <t>257164446390</t>
+  </si>
+  <si>
+    <t>1BỘ Ống 90-110mm Tốt</t>
+  </si>
+  <si>
+    <t>K239ONG90MMTOT</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>217289172762</t>
+  </si>
+  <si>
+    <t>1BỘ+Đế ống 100-110mm</t>
+  </si>
+  <si>
+    <t>1bo_ron_90_110mm_deK239</t>
+  </si>
+  <si>
+    <t>169000</t>
+  </si>
+  <si>
+    <t>25831963776</t>
+  </si>
+  <si>
+    <t>Bộ 8 Ke Góc Tam Giác Inox 1.4mm - Cố Định Góc 90  ∘   Ổn Định, Chắc Chắn K254</t>
+  </si>
+  <si>
+    <t>271944477983</t>
+  </si>
+  <si>
+    <t>Bộ 8 Ke+Vít</t>
+  </si>
+  <si>
+    <t>427275_bo_8_ke_vit</t>
+  </si>
+  <si>
+    <t>25841591992</t>
+  </si>
+  <si>
+    <t>BỘ 20 Tắc Kê Nở Sắt Cố Định Vật Dụng Trên Thạch Cao, Ván ép Chịu Lực Không Sợ Bung Rơi Khi Lắp Đặt K262</t>
+  </si>
+  <si>
+    <t>310376901607</t>
+  </si>
+  <si>
+    <t>Bộ 20 tắckê+vít K262</t>
+  </si>
+  <si>
+    <t>K262_BO20TACKETHACHCAO</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>26277431122</t>
+  </si>
+  <si>
+    <t>Công Tắc Cảm Biến Ánh Sáng Đèn Tự Động Sáng Khi Trời Tối Và Tự Tắt Khi Trời Sáng Giúp Tiết Kiệm Điện K263</t>
+  </si>
+  <si>
+    <t>252724980105</t>
+  </si>
+  <si>
+    <t>27438820291</t>
+  </si>
+  <si>
+    <t>Combo 4 Móc Inox Hình Chữ S Treo Đồ Nhà Bếp, Phòng Tắm, Treo Quần Áo Đa Năng K43</t>
+  </si>
+  <si>
+    <t>198603091975</t>
+  </si>
+  <si>
+    <t>COMBO 4 MÓC S</t>
+  </si>
+  <si>
+    <t>4MOC_INOXK43</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>27758197077</t>
+  </si>
+  <si>
+    <t>Giá Đỡ Vòi Hoa Sen Dán Tường K232 – Không Cần Khoan, Siêu Dính, Chịu Lực 10Kg</t>
+  </si>
+  <si>
+    <t>375017444364</t>
+  </si>
+  <si>
+    <t>Màu Bạc K232</t>
+  </si>
+  <si>
+    <t>K232-BAC</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>375017444365</t>
+  </si>
+  <si>
+    <t>Màu Xám K232</t>
+  </si>
+  <si>
+    <t>K232-XAM</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>375017444363</t>
+  </si>
+  <si>
+    <t>Màu Đen K232</t>
+  </si>
+  <si>
+    <t>K232-DEN</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>28014199899</t>
+  </si>
+  <si>
+    <t>Hộp 4 Bàn Chải Đánh Răng 3 Đầu Lông Mềm,Làm sạch răng toàn diện,Bảo vệ nướu răng,Giải Pháp Làm Sạch Răng Hiệu Quả K256</t>
+  </si>
+  <si>
+    <t>256787106973</t>
+  </si>
+  <si>
+    <t>1 Hộp 4 bàn chải</t>
+  </si>
+  <si>
+    <t>K256_BANCHAILONGMEM</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>15515891479</t>
-  </si>
-  <si>
-    <t>Nẹp Dây Điện Dán Tường Keo Nano Siêu Dính Thế Hệ Mới , Kẹp Dây Điện Cố Định an toàn tiện lợi dễ lắp đặt K110</t>
-  </si>
-  <si>
-    <t>203264569652</t>
-  </si>
-  <si>
-    <t>16 Nẹp Trong Đục Lớn</t>
-  </si>
-  <si>
-    <t>BO16TRONGDUCNEW-K110</t>
-  </si>
-  <si>
-    <t>187</t>
-  </si>
-  <si>
-    <t>203264569655</t>
-  </si>
-  <si>
-    <t>20 Nẹp Trong Đục Nhỏ</t>
-  </si>
-  <si>
-    <t>BO20MAUTRONGDUCNEW-K110</t>
-  </si>
-  <si>
-    <t>313</t>
-  </si>
-  <si>
-    <t>7690673333</t>
-  </si>
-  <si>
-    <t>Miếng Chặn Rác Silicone K20 – Ngăn Tắc Bồn Rửa, Đường Cống, Chống Tóc Rơi Xuống</t>
-  </si>
-  <si>
-    <t>82472964391</t>
-  </si>
-  <si>
-    <t>MIENGSILICON_BVCONGK20</t>
-  </si>
-  <si>
-    <t>2805379102</t>
-  </si>
-  <si>
-    <t>Bột/Thuốc Diệt Gián Sinh Học - Hiệu Quả Cực Mạnh, An Toàn Cho Gia Đình</t>
-  </si>
-  <si>
-    <t>31210759601</t>
-  </si>
-  <si>
-    <t>1 Bịch Diệt gián</t>
-  </si>
-  <si>
-    <t>1 BỊCH DIỆT GIÁN K154</t>
-  </si>
-  <si>
-    <t>15000</t>
-  </si>
-  <si>
-    <t>743</t>
-  </si>
-  <si>
-    <t>195866698283</t>
-  </si>
-  <si>
-    <t>3 Bịch Diệt gián</t>
-  </si>
-  <si>
-    <t>162613_combo_3_bich_diet_gian</t>
-  </si>
-  <si>
-    <t>247</t>
-  </si>
-  <si>
-    <t>257793964780</t>
-  </si>
-  <si>
-    <t>5BỊCH DIỆT GIÁN SALE</t>
-  </si>
-  <si>
-    <t>162612_combo_5_bich_diet_gian</t>
-  </si>
-  <si>
-    <t>55000</t>
-  </si>
-  <si>
-    <t>5381318046</t>
-  </si>
-  <si>
-    <t>Găng Tay Chống Nóng Lò Nướng K018 – Dày Dặn, Cách Nhiệt Tốt, An Toàn Khi Làm Bán</t>
-  </si>
-  <si>
-    <t>34051322550</t>
-  </si>
-  <si>
-    <t>GANGTAY_LAMBANHK18</t>
-  </si>
-  <si>
-    <t>32000</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>2907252325</t>
-  </si>
-  <si>
-    <t>Đui Đèn Thông Minh E27 Điều Khiển Từ Xa, 5 Mức Hẹn Giờ Tắt, Kèm Remote + Pin, Không Cần Cài Đặt K84</t>
-  </si>
-  <si>
-    <t>290174216058</t>
-  </si>
-  <si>
-    <t>1 ĐUI ĐÈN DK K84</t>
-  </si>
-  <si>
-    <t>MOCDAN_TRONGSUOTK84</t>
-  </si>
-  <si>
-    <t>1_dui_den_dk_k84</t>
-  </si>
-  <si>
-    <t>3356099336</t>
-  </si>
-  <si>
-    <t>COMBO 3 Móc dán tường Cao Cấp kẹp giữ cây lau nhà , móc treo chổi chịu lực 6kg - K48</t>
-  </si>
-  <si>
-    <t>271839669458</t>
-  </si>
-  <si>
-    <t>COMBO 3 MÓC</t>
-  </si>
-  <si>
-    <t>K48</t>
-  </si>
-  <si>
-    <t>400347_combo_3_moc</t>
-  </si>
-  <si>
-    <t>29000</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>7456001637</t>
-  </si>
-  <si>
-    <t>Áo Trùm Máy Giặt Cao Cấp Chống Thấm Nước ,chống Bám Bụi Mẫu Mã Đa Dạng Đẹp Và Sang Trọng Lắp Đặt Dễ Dàng K142</t>
-  </si>
-  <si>
-    <t>164368356462</t>
-  </si>
-  <si>
-    <t>Cửa Trên 5KG Mèo</t>
-  </si>
-  <si>
-    <t>CUATREN5KGMEO</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>108909146879</t>
-  </si>
-  <si>
-    <t>Cửa Trên 5KG ĐDương</t>
-  </si>
-  <si>
-    <t>TREN5KGDAIDUONG</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>48633594528</t>
-  </si>
-  <si>
-    <t>CửangangMèo 65x67x87</t>
-  </si>
-  <si>
-    <t>65X67X87NGANGMEO</t>
-  </si>
-  <si>
-    <t>110000</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>108909146889</t>
-  </si>
-  <si>
-    <t>CỬATRÊNDD 65X65X105</t>
-  </si>
-  <si>
-    <t>TREN65X65X105DAIDUONG</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>38634334554</t>
-  </si>
-  <si>
-    <t>Cửa ngang 7KG Mèo</t>
-  </si>
-  <si>
-    <t>CUANGANG7KGMEO</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>108909146882</t>
-  </si>
-  <si>
-    <t>Cửa ngang 7KG ĐDương</t>
-  </si>
-  <si>
-    <t>CUANGANG7KGDAIDUONG</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>38634334556</t>
-  </si>
-  <si>
-    <t>Cửa trên 7KG Mèo</t>
-  </si>
-  <si>
-    <t>CUATREN7KGMEO</t>
-  </si>
-  <si>
-    <t>164368356467</t>
-  </si>
-  <si>
-    <t>CửaTrênMèo 65x65x105</t>
-  </si>
-  <si>
-    <t>CUATRENMEO65X65X105</t>
-  </si>
-  <si>
-    <t>108909146880</t>
-  </si>
-  <si>
-    <t>Cửangang ĐD 65X67X87</t>
-  </si>
-  <si>
-    <t>65X67X87NGANGDAIDUONG</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>108909146891</t>
-  </si>
-  <si>
-    <t>Cửa trên 7KG DDương</t>
-  </si>
-  <si>
-    <t>TREN7KGDAIDUONG</t>
-  </si>
-  <si>
-    <t>4548364452</t>
-  </si>
-  <si>
-    <t>COMBO 12 KẸP DÁN CỐ ĐỊNH DÂY CÁP SẠC,DÂY ĐIỆN GIÚP LÀM GỌN GÀNG DÂY ĐIỆN K72</t>
-  </si>
-  <si>
-    <t>249164749142</t>
-  </si>
-  <si>
-    <t>COMBO 1 KẸP TRẮNGK72</t>
-  </si>
-  <si>
-    <t>526675_combo_1_kep_trangk72</t>
-  </si>
-  <si>
-    <t>249164749143</t>
-  </si>
-  <si>
-    <t>COMBO 12 KẸP ĐENK72</t>
-  </si>
-  <si>
-    <t>526675_combo_12_kep_denk72</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>4848363969</t>
-  </si>
-  <si>
-    <t>Miếng Dán Gắn Ổ Cắm, Thiết Bị Điện – Siêu Dính, Dễ Tháo Lắp K059</t>
-  </si>
-  <si>
-    <t>64453593966</t>
-  </si>
-  <si>
-    <t>Màu Xám</t>
-  </si>
-  <si>
-    <t>ChihuyT069</t>
-  </si>
-  <si>
-    <t>K059_THANHTRUOTXAM</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>64453593967</t>
-  </si>
-  <si>
-    <t>Màu Trắng</t>
-  </si>
-  <si>
-    <t>K059_THANHTRUOTTRANG</t>
-  </si>
-  <si>
-    <t>5451944240</t>
-  </si>
-  <si>
-    <t>Thuốc diệt gián Nội Địa Hiểu Qủa Nhanh Chóng Trọng Lượng 1 Gói 5g K154</t>
-  </si>
-  <si>
-    <t>168754313020</t>
-  </si>
-  <si>
-    <t>dietgian</t>
-  </si>
-  <si>
-    <t>185866720568</t>
-  </si>
-  <si>
-    <t>71037223628</t>
-  </si>
-  <si>
-    <t>1Bịch Diệt gián</t>
-  </si>
-  <si>
-    <t>14008640325</t>
-  </si>
-  <si>
-    <t>Cọ Vệ Sinh Khe Cửa Sổ 2 Trong 1 K012 – Đa Năng, Làm Sạch Mọi Ngóc Ngách</t>
-  </si>
-  <si>
-    <t>37911997623</t>
-  </si>
-  <si>
-    <t>COLAMSACH_K12</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>11135551865</t>
-  </si>
-  <si>
-    <t>Mũ Gội Đầu Cho Bé K62 – Chống Nước Vào Mắt, Êm Đầu, Xốp Mềm Co Giãn</t>
-  </si>
-  <si>
-    <t>300123893866</t>
-  </si>
-  <si>
-    <t>Màu Hồng</t>
-  </si>
-  <si>
-    <t>MUGOIDAU_DETHUONGK62</t>
-  </si>
-  <si>
-    <t>mau_hong K62</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>300123893865</t>
-  </si>
-  <si>
-    <t>Màu Vàng</t>
-  </si>
-  <si>
-    <t>mau_vang K62</t>
-  </si>
-  <si>
-    <t>5948362499</t>
-  </si>
-  <si>
-    <t>[Bộ 20/16] Nẹp Dây Điện Dán Tường Trong Suốt - Kẹp Cố Định Dây Điện/Cáp Mạng Thông Minh, Giữ Nhà Cửa Gọn Gàng K145</t>
-  </si>
-  <si>
-    <t>249134430410</t>
-  </si>
-  <si>
-    <t>20 Nẹp Trong Đục NEW</t>
-  </si>
-  <si>
-    <t>BO20TRONGDUCK110</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>249134430411</t>
-  </si>
-  <si>
-    <t>16 Nẹp Trong Đục NEW</t>
-  </si>
-  <si>
-    <t>BO16TRONGDUCK110</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>249134430408</t>
-  </si>
-  <si>
-    <t>Bộ 20 Nẹp Nhỏ + Keo</t>
-  </si>
-  <si>
-    <t>BO20TRONGSUOT</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>249134430409</t>
-  </si>
-  <si>
-    <t>Bộ 16 Nẹp Lớn + Keo</t>
-  </si>
-  <si>
-    <t>BO16TRONGSUOT</t>
-  </si>
-  <si>
-    <t>6064773742</t>
-  </si>
-  <si>
-    <t>Màng Lọc Dầu Mỡ Máy Hút Mùi K153 – Giữ Bếp Sạch, Chống Bám Bẩn Hiệu Quả</t>
-  </si>
-  <si>
-    <t>41950199165</t>
-  </si>
-  <si>
-    <t>MANGLOC_CHANDAUMO</t>
-  </si>
-  <si>
-    <t>18000</t>
-  </si>
-  <si>
-    <t>8882127653</t>
-  </si>
-  <si>
-    <t>Cuộn 17 Túi Rác Tự Hủy Sinh Học K101 – Mỏng, Bền, Thân Thiện Môi Trường</t>
-  </si>
-  <si>
-    <t>101149234142</t>
-  </si>
-  <si>
-    <t>TUIRAC_TUHUYK101</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>6856001620</t>
-  </si>
-  <si>
-    <t>Bọc Tủ Lạnh K144 – Chống Nước, Chống Bụi, Có Túi 2 Bên Tiện Lợi</t>
-  </si>
-  <si>
-    <t>300002545460</t>
-  </si>
-  <si>
-    <t>Hình Đại Dương,130cm x 55cm</t>
-  </si>
-  <si>
-    <t>BOC_TULANH</t>
-  </si>
-  <si>
-    <t>249692_hinh_dai_duong_130cm_x_55cm</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>164360512854</t>
-  </si>
-  <si>
-    <t>Hình Con Mèo,130cm x 55cm</t>
-  </si>
-  <si>
-    <t>BOCTULANH_MEO</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>164360512855</t>
-  </si>
-  <si>
-    <t>Hình Con Thỏ,130cm x 55cm</t>
-  </si>
-  <si>
-    <t>BOCTULANH_THO</t>
-  </si>
-  <si>
-    <t>7037990835</t>
-  </si>
-  <si>
-    <t>Combo 5 Chốt Cửa Tủ inox dày 0.8mm (Roller Catch) - Lắp Đặt Nhanh, Đóng Êm Ái K023</t>
-  </si>
-  <si>
-    <t>330078341967</t>
-  </si>
-  <si>
-    <t>COMBO 5 CHỐT 7 MÀU</t>
-  </si>
-  <si>
-    <t>combo_5_chot_7_mau</t>
-  </si>
-  <si>
-    <t>249019174211</t>
-  </si>
-  <si>
-    <t>COMBO 5 CHỐT BẠC</t>
-  </si>
-  <si>
-    <t>combo_5_chot_bac</t>
+    <t>28088816952</t>
+  </si>
+  <si>
+    <t>Cốc Dán Tường Hình Gấu Đựng Bàn Chải Kem Đánh Răng – Gọn Gàng, Dễ Thương K149</t>
+  </si>
+  <si>
+    <t>227945211207</t>
+  </si>
+  <si>
+    <t>1 Cốc Gấu K149</t>
+  </si>
+  <si>
+    <t>COCGAU_K149</t>
   </si>
   <si>
     <t>84</t>
   </si>
   <si>
-    <t>7623356102</t>
-  </si>
-  <si>
-    <t>Bộ 10 Đôi Đũa Khắc Họa Tiết Hoa Anh Đào Chống Mốc Chống Trơn Trượt Độ Dài 24cm và 27cm - K054</t>
-  </si>
-  <si>
-    <t>176458351242</t>
-  </si>
-  <si>
-    <t>Đũa Hoa Anh Đào 24cm</t>
-  </si>
-  <si>
-    <t>duahopkim</t>
-  </si>
-  <si>
-    <t>K54HOAANHDAO24CM</t>
-  </si>
-  <si>
-    <t>65000</t>
-  </si>
-  <si>
-    <t>298</t>
-  </si>
-  <si>
-    <t>225208121707</t>
-  </si>
-  <si>
-    <t>Đũa Hoa Anh Đào 27cm</t>
-  </si>
-  <si>
-    <t>K54HOAANHDAO27CM</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>11135553238</t>
-  </si>
-  <si>
-    <t>Kệ Để Đồ Nhà Bếp &amp; Phòng Tắm Nhôm Không Rỉ – Chịu Lực 30kg – Dán Tường K108</t>
-  </si>
-  <si>
-    <t>207227212403</t>
-  </si>
-  <si>
-    <t>CHỮ NHẬT 2 LỚP BẠC</t>
-  </si>
-  <si>
-    <t>THANHCHANCUA_MUTXOPK108</t>
-  </si>
-  <si>
-    <t>K108_CNMAUBAC</t>
-  </si>
-  <si>
-    <t>139000</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>207227212404</t>
-  </si>
-  <si>
-    <t>TAM GIÁC 2 LỚP BẠC</t>
-  </si>
-  <si>
-    <t>K108_TGMAUBAC</t>
-  </si>
-  <si>
-    <t>207227212401</t>
-  </si>
-  <si>
-    <t>CHỮ NHẬT 3 LỚP ĐEN</t>
-  </si>
-  <si>
-    <t>K108_CNMAUDEN</t>
-  </si>
-  <si>
-    <t>207227212402</t>
-  </si>
-  <si>
-    <t>TAM GIÁC 3 LỚP ĐEN</t>
-  </si>
-  <si>
-    <t>K108_TGMAUDEN</t>
-  </si>
-  <si>
-    <t>13615381825</t>
-  </si>
-  <si>
-    <t>Bộ 100 Đinh 2 Đầu Dùng Để Đóng Chân Tường ,Tủ Kệ Bếp Che Khuyết Điểm K97</t>
-  </si>
-  <si>
-    <t>127878289683</t>
-  </si>
-  <si>
-    <t>Bộ 100 Đinh + ống</t>
-  </si>
-  <si>
-    <t>K97_100DINH2DAU</t>
-  </si>
-  <si>
-    <t>7756001691</t>
-  </si>
-  <si>
-    <t>Tạp Dề, Yếm Nấu Ăn ,Học Vẽ Có Lót Tay, Chống Thấm Nước Loại Đẹp K07</t>
-  </si>
-  <si>
-    <t>164727386290</t>
-  </si>
-  <si>
-    <t>Size Nhí ( Xanh)</t>
-  </si>
-  <si>
-    <t>ChihuyT078</t>
-  </si>
-  <si>
-    <t>TAPDENHIXANHK07</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>164727386291</t>
-  </si>
-  <si>
-    <t>Size Nhí ( Vàng)</t>
-  </si>
-  <si>
-    <t>TAPDENHIVANGK07</t>
-  </si>
-  <si>
-    <t>155972301739</t>
-  </si>
-  <si>
-    <t>Màu Xanh Hồng</t>
-  </si>
-  <si>
-    <t>TAPDEXANHHONGK07</t>
-  </si>
-  <si>
-    <t>155972301740</t>
-  </si>
-  <si>
-    <t>Màu Nâu Xanh</t>
-  </si>
-  <si>
-    <t>TAPDENAUXANHK07</t>
-  </si>
-  <si>
-    <t>8690874835</t>
-  </si>
-  <si>
-    <t>Khăn Lau Đa Năng Microfiber K074 – Dày Dặn, Hút Nước Gấp 3 Lần</t>
-  </si>
-  <si>
-    <t>47065318525</t>
-  </si>
-  <si>
-    <t>KHANLAU_OTOK74</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>8788662942</t>
-  </si>
-  <si>
-    <t>Set 10 NẸP LÁ DÁN TƯỜNG – Giữ Dây Gọn Gàng, Dán Cây Cực Chắc, KHÔNG CẦN KHOAN!</t>
-  </si>
-  <si>
-    <t>275975546309</t>
-  </si>
-  <si>
-    <t>10 NẸP LÁ CÂY + KEO</t>
-  </si>
-  <si>
-    <t>MIENGDAN_PHANTANGK118</t>
-  </si>
-  <si>
-    <t>10_nep_hinh_la_cayK109</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>18767750537</t>
-  </si>
-  <si>
-    <t>Băng Dính Gai Làm Gọn Dây Điện, Băng Dán Gai Đa Năng Băng Nhám Làm Gọn Góc Pc, Dây Cáp Sạc, Tai Nghe K205</t>
-  </si>
-  <si>
-    <t>213491275436</t>
-  </si>
-  <si>
-    <t>1 Cuộn Dài 1,5M</t>
-  </si>
-  <si>
-    <t>BANGDINH_K205</t>
-  </si>
-  <si>
-    <t>24768421006</t>
-  </si>
-  <si>
-    <t>COMBO 20 Tắc Kê Sắt + 20 Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
-  </si>
-  <si>
-    <t>415230669086</t>
-  </si>
-  <si>
-    <t>20 Bộ KT 6mm X 32mm</t>
-  </si>
-  <si>
-    <t>BO20TACKE6X32MMK243</t>
-  </si>
-  <si>
-    <t>85000</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>415230669087</t>
-  </si>
-  <si>
-    <t>20 Bộ KT 8mm X 60mm</t>
-  </si>
-  <si>
-    <t>20BOKT 8mmX60mm K243</t>
-  </si>
-  <si>
-    <t>135000</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>415230669085</t>
-  </si>
-  <si>
-    <t>20 Bộ KT 5mm X 30mm</t>
-  </si>
-  <si>
-    <t>20BOTACKE5X30MMK243</t>
-  </si>
-  <si>
-    <t>75000</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>9523434925</t>
-  </si>
-  <si>
-    <t>Dũa Móng Tay 6 Mặt K106 – Vừa Chà Nhám Vừa Đánh Bóng, Móng Mịn Như Spa</t>
-  </si>
-  <si>
-    <t>44051336796</t>
-  </si>
-  <si>
-    <t>DUAMONGTAY_6MATK106</t>
-  </si>
-  <si>
-    <t>10335548632</t>
-  </si>
-  <si>
-    <t>Túi Đựng Rác Tự Phân Hủy K70 – Có Dây Rút, Sạch Sẽ, Thân Thiện Môi Trường</t>
-  </si>
-  <si>
-    <t>84441035566</t>
-  </si>
-  <si>
-    <t>TUIRAC_DAYRUTK70</t>
-  </si>
-  <si>
-    <t>24478477879</t>
-  </si>
-  <si>
-    <t>Chai Xịt Vệ Sinh Dạng Bọt Tuyết Tẩy Rửa Nhà Bếp Siêu Đa Năng,Tẩy Sạch Vết Dầu Mỡ Cứng Đầu Global 500ml - K46</t>
-  </si>
-  <si>
-    <t>255766638889</t>
-  </si>
-  <si>
-    <t>1 chai 500ml</t>
-  </si>
-  <si>
-    <t>K46_CHAIXITVESINHBEP</t>
-  </si>
-  <si>
-    <t>119000</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>11076966036</t>
-  </si>
-  <si>
-    <t>Keo Chống Thấm Thế Hệ Mới GOSU Thời Gian Khô Nhanh Chóng Thích Hợp Quét Ngoài Trời ,Sân Thượng K162</t>
-  </si>
-  <si>
-    <t>242926384187</t>
-  </si>
-  <si>
-    <t>1 TÚI KEO 500ML K162</t>
-  </si>
-  <si>
-    <t>K162_KEOCHONGTHAM500ML</t>
-  </si>
-  <si>
-    <t>735</t>
-  </si>
-  <si>
-    <t>11708283596</t>
-  </si>
-  <si>
-    <t>100 Sợi Dây Rút Nhựa Dài 100mm và 200mm - K36</t>
-  </si>
-  <si>
-    <t>258985454594</t>
-  </si>
-  <si>
-    <t>100 Dây Dài 100mm</t>
-  </si>
-  <si>
-    <t>DAYRUT_K36</t>
-  </si>
-  <si>
-    <t>400348_100_day_dai_100mm</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>258985454595</t>
-  </si>
-  <si>
-    <t>100 Dây Dài 200mm</t>
-  </si>
-  <si>
-    <t>400348_100_day_dai_200mm</t>
-  </si>
-  <si>
-    <t>12015405187</t>
-  </si>
-  <si>
-    <t>Công Tắc Cảm Biến Ánh Sáng K263 Tự Động Bật Đèn Khi Trời Tối – Tắt Khi Trời Sáng Tiết Kiệm Điện Cho Ngoài Trời</t>
-  </si>
-  <si>
-    <t>128395394060</t>
-  </si>
-  <si>
-    <t>1 Bộ  AS10K263</t>
-  </si>
-  <si>
-    <t>MOCNHUA_TREOQUANAOK78</t>
-  </si>
-  <si>
-    <t>K263-AS10</t>
-  </si>
-  <si>
-    <t>260</t>
-  </si>
-  <si>
-    <t>12220381107</t>
-  </si>
-  <si>
-    <t>Bộ 10 miếng dán cố định thảm lót sàn ô tô - Chống trơn trượt, tái sử dụng nhiều lần K116</t>
-  </si>
-  <si>
-    <t>237531224352</t>
-  </si>
-  <si>
-    <t>COMBO 10MIẾNG 5X5CM</t>
-  </si>
-  <si>
-    <t>MIENGDANKEO_2MATK116</t>
-  </si>
-  <si>
-    <t>167477_combo_10mieng_5x5cm</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>13315378460</t>
-  </si>
-  <si>
-    <t>Cuộn Ron Cửa Chặn Khe Hở Ngăn Bụi,Nước,Côn Trùng, Cách Âm Chất Liệu TPE Cao Cấp K75</t>
-  </si>
-  <si>
-    <t>218229468769</t>
-  </si>
-  <si>
-    <t>5CM X 1M MÀU XÁM K75</t>
-  </si>
-  <si>
-    <t>CUONRON_CUACHONGONK75</t>
-  </si>
-  <si>
-    <t>K75_MAUXAM5CM1M</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>218229468770</t>
-  </si>
-  <si>
-    <t>5CM X 1M MÀU NÂU K75</t>
-  </si>
-  <si>
-    <t>K75_MAUNAU5CM1M</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>218229468768</t>
-  </si>
-  <si>
-    <t>5CMX1M MÀU TRẮNG K75</t>
-  </si>
-  <si>
-    <t>K75_MAUTRANG5CM1M</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>14108638821</t>
-  </si>
-  <si>
-    <t>Cây Cọ Rửa Ly Cốc Silicon K013 – Tạo Bọt, Không Trầy, Dùng Được Cho Bình Sữa</t>
-  </si>
-  <si>
-    <t>122624695768</t>
-  </si>
-  <si>
-    <t>màu ngẫu nhiên</t>
-  </si>
-  <si>
-    <t>CAYCOSILICON_K13</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>14109452622</t>
-  </si>
-  <si>
-    <t>Túi Vải Chia Ngăn Đựng Đồ Lót Tất Vớ K026 – Gấp Gọn, Dễ Tìm, Dễ Sắp Xếp</t>
-  </si>
-  <si>
-    <t>28257567996</t>
-  </si>
-  <si>
-    <t>Túi Vải 11 ngăn</t>
-  </si>
-  <si>
-    <t>TUIVAI11NGANK26</t>
-  </si>
-  <si>
-    <t>114195866554</t>
-  </si>
-  <si>
-    <t>Túi Vải 6 ngăn</t>
-  </si>
-  <si>
-    <t>TUIVAIDUNGDO_6NGANK26</t>
-  </si>
-  <si>
-    <t>114195866555</t>
-  </si>
-  <si>
-    <t>Túi Vải 7 ngăn</t>
-  </si>
-  <si>
-    <t>TUIVAIDUNGDO_7NGANK26</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>14677195925</t>
-  </si>
-  <si>
-    <t>Gioăng Bồn Cầu Ngăn Mùi Hôi, Ngăn Côn Trùng – Linh Kiện Cực Cần Khi Lắp Bồn Cầu K168</t>
-  </si>
-  <si>
-    <t>147762755036</t>
-  </si>
-  <si>
-    <t>1 Bộ Ống 100-110mm</t>
-  </si>
-  <si>
-    <t>BO100-110mmK168</t>
-  </si>
-  <si>
-    <t>239000</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>15477291455</t>
-  </si>
-  <si>
-    <t>Bàn Chải Lông Mềm, Không Làm Tổn Thương Quần Áo, Giày Dép,Vệ Sinh Đa Năng, Cọ Rửa Giày, Cọ Rửa Gia Dụng Cao Cấp K172</t>
-  </si>
-  <si>
-    <t>138299343386</t>
-  </si>
-  <si>
-    <t>Màu Xanh Dương K172</t>
-  </si>
-  <si>
-    <t>mau_xanh_duong_k172</t>
-  </si>
-  <si>
-    <t>138299343387</t>
-  </si>
-  <si>
-    <t>Màu Xám K172</t>
-  </si>
-  <si>
-    <t>mau_xam_k172</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>17595269902</t>
-  </si>
-  <si>
-    <t>Viên Thả Bồn Cầu 3IN1 Vừa Vệ Sinh ,Diệt Vi Khuẩn,Làm Bóng Men Sứ Bồn Cầu Vừa Tỏa Hương Thơm Mát Mẫu Mới K222</t>
-  </si>
-  <si>
-    <t>395510815655</t>
-  </si>
-  <si>
-    <t>COMBO 5 VIÊN 3IN1</t>
-  </si>
-  <si>
-    <t>COMBO5VIEN3IN1K222</t>
-  </si>
-  <si>
-    <t>223</t>
-  </si>
-  <si>
-    <t>395510815656</t>
-  </si>
-  <si>
-    <t>COMBO 10 VIÊN 3IN1</t>
-  </si>
-  <si>
-    <t>COMBO10VIENK222</t>
-  </si>
-  <si>
-    <t>165000</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>18314797680</t>
-  </si>
-  <si>
-    <t>Ron Chặn Khe Cửa Giảm Tiếng Ồn Chất Liệu TPE  – Thanh Chắn Khe Hở Chống Gió Lùa, Giữ Nhiệt Điều Hòa K185</t>
-  </si>
-  <si>
-    <t>435548140513</t>
-  </si>
-  <si>
-    <t>1Cuộn Nâu 5cm x 2M</t>
-  </si>
-  <si>
-    <t>NAU_5cmx2mK185</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>435548140514</t>
-  </si>
-  <si>
-    <t>1Cuộn Xám 5cm x 2M</t>
-  </si>
-  <si>
-    <t>XAM_5cmx2mK185</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>435548140515</t>
-  </si>
-  <si>
-    <t>1Cuộn Trắng 5cmx2M</t>
-  </si>
-  <si>
-    <t>TRANG_5cmx2mK185</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>265476202386</t>
-  </si>
-  <si>
-    <t>1Cuộn Nâu 3,5cm x 2M</t>
-  </si>
-  <si>
-    <t>NAU_3,5cmx2mK185</t>
-  </si>
-  <si>
-    <t>198</t>
-  </si>
-  <si>
-    <t>265476202387</t>
-  </si>
-  <si>
-    <t>1Cuộn Xám 3,5cm x 2M</t>
-  </si>
-  <si>
-    <t>XAM_3,5cmx2mK185</t>
-  </si>
-  <si>
-    <t>435548140512</t>
-  </si>
-  <si>
-    <t>1Cuộn Trắng 3,5cmx2M</t>
-  </si>
-  <si>
-    <t>TRANG_3,5cmx2mK185</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>19660248478</t>
-  </si>
-  <si>
-    <t>Thước Dây Cuộn Đo 3 Vòng Tự Động Chỉ Cần 1 Nút Bấm giúp Quản Lí Số Đo Cơ Thể Mỗi Ngày K204</t>
-  </si>
-  <si>
-    <t>203074115330</t>
-  </si>
-  <si>
-    <t>THUOCDAY_K204</t>
-  </si>
-  <si>
-    <t>27181536554</t>
-  </si>
-  <si>
-    <t>Mũi Khoan Lệch Tâm Đa Năng Chuyên Khoan Gạch Men Cứng, Gỗ, Tường, KimLoại All In One Khoan Nhanh Và Nhẹ K265</t>
-  </si>
-  <si>
-    <t>237603798078</t>
-  </si>
-  <si>
-    <t>1 MŨIKHOAN 12MM K265</t>
-  </si>
-  <si>
-    <t>1_muikhoan_12mm_k265</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>237603798079</t>
-  </si>
-  <si>
-    <t>COMBO 6-8-10-12MM</t>
-  </si>
-  <si>
-    <t>205706_combo_4_mui_6_8_10_12mm_k265</t>
-  </si>
-  <si>
-    <t>125000</t>
-  </si>
-  <si>
-    <t>237603798075</t>
-  </si>
-  <si>
-    <t>1 MŨI KHOAN 6MM K265</t>
-  </si>
-  <si>
-    <t>1_mui_khoan_6mm_k265</t>
-  </si>
-  <si>
-    <t>237603798076</t>
-  </si>
-  <si>
-    <t>1 MŨI KHOAN 8MM K265</t>
-  </si>
-  <si>
-    <t>1_mui_khoan_8mm_k265</t>
-  </si>
-  <si>
-    <t>33000</t>
-  </si>
-  <si>
-    <t>237603798077</t>
-  </si>
-  <si>
-    <t>1 MŨIKHOAN 10MM K265</t>
-  </si>
-  <si>
-    <t>1_muikhoan_10mm_k265</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>21428120893</t>
-  </si>
-  <si>
-    <t>Móc Inox Dán Tường Siêu Dính Treo Thau Chậu, Nồi ,Thớt , Khăn, Quần Áo/ Giá Gắn Tường Treo Đồ Nhà Bếp, Nhà Tắm K190</t>
-  </si>
-  <si>
-    <t>181456809001</t>
-  </si>
-  <si>
-    <t>MOCDANTUONGTREOTHAU_K190</t>
-  </si>
-  <si>
-    <t>22000</t>
-  </si>
-  <si>
-    <t>22327610052</t>
-  </si>
-  <si>
-    <t>Dụng Cụ Đa Năng Mở Nắp Tất Cả Đồ Hộp Dễ Dàng Và Nhanh Chóng K210</t>
-  </si>
-  <si>
-    <t>146663161285</t>
-  </si>
-  <si>
-    <t>Màu Ngẫu Nhiên</t>
-  </si>
-  <si>
-    <t>DUNGCUMONAP_K210</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>25277881916</t>
-  </si>
-  <si>
-    <t>Đầu Nam Châm Gắn Mũi Bắt Vít Siêu Hít Chất Liệu Thép Hợp Kim S2 Siêu Bền giúp giữ chặt vít khi siết không sợ rớt K245</t>
-  </si>
-  <si>
-    <t>236290515417</t>
-  </si>
-  <si>
-    <t>1 Cái Đầu Nam Châm</t>
-  </si>
-  <si>
-    <t>K245_DAUNAMCHAMBATVIT</t>
-  </si>
-  <si>
-    <t>24428476358</t>
-  </si>
-  <si>
-    <t>Nước Giặt Đồ Lót Nano Bạc K252 – Khử Mùi, Kháng Khuẩn, Ngăn Viêm Nhiễm Hiệu Quả</t>
-  </si>
-  <si>
-    <t>147290375577</t>
-  </si>
-  <si>
-    <t>1 Chai 300ml</t>
-  </si>
-  <si>
-    <t>K252_NUOCGIATDOLOT</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>24559734917</t>
-  </si>
-  <si>
-    <t>Combo 5 Miếng thép sửa bản lề tủ, miếng sửa bản lề tủ, tấm thép sửa bản lề dễ dàng và tiết kiệm chi phí K237</t>
-  </si>
-  <si>
-    <t>320375059047</t>
-  </si>
-  <si>
-    <t>COMBO 5 MIẾNG K237</t>
-  </si>
-  <si>
-    <t>305410_5_mieng_hinh_vuong</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>25006646227</t>
-  </si>
-  <si>
-    <t>Dụng Cụ Bịt Kín Ống Thoát Nước Silicone – Chống Mùi, Chống Côn Trùng – Siêu Êm, Siêu Bền K258</t>
-  </si>
-  <si>
-    <t>440327644402</t>
-  </si>
-  <si>
-    <t>1 BỘ ỐNG 45-50MM</t>
-  </si>
-  <si>
-    <t>K258_45-50MM</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>440327644403</t>
-  </si>
-  <si>
-    <t>1 BỘ ỐNG 60-65MM</t>
-  </si>
-  <si>
-    <t>K258_60-65MM</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>440327644401</t>
-  </si>
-  <si>
-    <t>1 BỘ ỐNG 35-40MM</t>
-  </si>
-  <si>
-    <t>K258_35-40MM</t>
-  </si>
-  <si>
-    <t>70000</t>
-  </si>
-  <si>
-    <t>193</t>
-  </si>
-  <si>
-    <t>25060391669</t>
-  </si>
-  <si>
-    <t>Gioăng Khử Mùi Hôi Bồn Cầu Cao Cấp, Ron Chống Hôi Bồn Cầu Dụng Cụ Không Thể Thiếu Khi Lắp Đặt Bồn Cầu K239</t>
-  </si>
-  <si>
-    <t>217289172762</t>
-  </si>
-  <si>
-    <t>1BỘ+Đế ống 100-110mm</t>
-  </si>
-  <si>
-    <t>1bo_ron_90_110mm_deK239</t>
-  </si>
-  <si>
-    <t>169000</t>
-  </si>
-  <si>
-    <t>257164446390</t>
-  </si>
-  <si>
-    <t>1BỘ Ống 90-110mm Tốt</t>
-  </si>
-  <si>
-    <t>K239ONG90MMTOT</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>25831963776</t>
-  </si>
-  <si>
-    <t>Bộ 8 Ke Góc Tam Giác Inox 1.4mm - Cố Định Góc 90  ∘   Ổn Định, Chắc Chắn K254</t>
-  </si>
-  <si>
-    <t>271944477983</t>
-  </si>
-  <si>
-    <t>Bộ 8 Ke+Vít</t>
-  </si>
-  <si>
-    <t>427275_bo_8_ke_vit</t>
-  </si>
-  <si>
-    <t>25841591992</t>
-  </si>
-  <si>
-    <t>BỘ 20 Tắc Kê Nở Sắt Cố Định Vật Dụng Trên Thạch Cao, Ván ép Chịu Lực Không Sợ Bung Rơi Khi Lắp Đặt K262</t>
-  </si>
-  <si>
-    <t>310376901607</t>
-  </si>
-  <si>
-    <t>Bộ 20 tắckê+vít K262</t>
-  </si>
-  <si>
-    <t>K262_BO20TACKETHACHCAO</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>26277431122</t>
-  </si>
-  <si>
-    <t>Công Tắc Cảm Biến Ánh Sáng Đèn Tự Động Sáng Khi Trời Tối Và Tự Tắt Khi Trời Sáng Giúp Tiết Kiệm Điện K263</t>
-  </si>
-  <si>
-    <t>252724980105</t>
-  </si>
-  <si>
-    <t>27438820291</t>
-  </si>
-  <si>
-    <t>Combo 4 Móc Inox Hình Chữ S Treo Đồ Nhà Bếp, Phòng Tắm, Treo Quần Áo Đa Năng K43</t>
-  </si>
-  <si>
-    <t>198603091975</t>
-  </si>
-  <si>
-    <t>COMBO 4 MÓC S</t>
-  </si>
-  <si>
-    <t>4MOC_INOXK43</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>27758197077</t>
-  </si>
-  <si>
-    <t>Giá Đỡ Vòi Hoa Sen Dán Tường K232 – Không Cần Khoan, Siêu Dính, Chịu Lực 10Kg</t>
-  </si>
-  <si>
-    <t>375017444365</t>
-  </si>
-  <si>
-    <t>Màu Xám K232</t>
-  </si>
-  <si>
-    <t>K232-XAM</t>
-  </si>
-  <si>
-    <t>375017444363</t>
-  </si>
-  <si>
-    <t>Màu Đen K232</t>
-  </si>
-  <si>
-    <t>K232-DEN</t>
-  </si>
-  <si>
-    <t>273</t>
-  </si>
-  <si>
-    <t>375017444364</t>
-  </si>
-  <si>
-    <t>Màu Bạc K232</t>
-  </si>
-  <si>
-    <t>K232-BAC</t>
-  </si>
-  <si>
-    <t>28014199899</t>
-  </si>
-  <si>
-    <t>Hộp 4 Bàn Chải Đánh Răng 3 Đầu Lông Mềm,Làm sạch răng toàn diện,Bảo vệ nướu răng,Giải Pháp Làm Sạch Răng Hiệu Quả K256</t>
-  </si>
-  <si>
-    <t>256787106973</t>
-  </si>
-  <si>
-    <t>1 Hộp 4 bàn chải</t>
-  </si>
-  <si>
-    <t>K256_BANCHAILONGMEM</t>
-  </si>
-  <si>
-    <t>28088816952</t>
-  </si>
-  <si>
-    <t>Cốc Dán Tường Hình Gấu Đựng Bàn Chải Kem Đánh Răng – Gọn Gàng, Dễ Thương K149</t>
-  </si>
-  <si>
-    <t>227945211207</t>
-  </si>
-  <si>
-    <t>1 Cốc Gấu K149</t>
-  </si>
-  <si>
-    <t>COCGAU_K149</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
     <t>28534548930</t>
   </si>
   <si>
@@ -2200,9 +2200,6 @@
     <t>210000</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
     <t>157813223177</t>
   </si>
   <si>
@@ -2230,7 +2227,7 @@
     <t>40TACKE8X60MMK243</t>
   </si>
   <si>
-    <t>225</t>
+    <t>222</t>
   </si>
   <si>
     <t>370230821234</t>
@@ -2242,7 +2239,7 @@
     <t>40TACKE5X30MM</t>
   </si>
   <si>
-    <t>124</t>
+    <t>122</t>
   </si>
   <si>
     <t>370230821235</t>
@@ -2260,21 +2257,48 @@
     <t>Dụng Cụ Ngăn Mùi Ống Thoát Nước K258 Cho Bồn Rửa, Lavabo, Máy Giặt – Chống Mùi Hôi &amp; Côn Trùng</t>
   </si>
   <si>
+    <t>297272665239</t>
+  </si>
+  <si>
     <t>297272665240</t>
   </si>
   <si>
     <t>297272665238</t>
   </si>
   <si>
-    <t>297272665239</t>
-  </si>
-  <si>
     <t>29338816641</t>
   </si>
   <si>
     <t>Túi Hút Chân Không Bảo Quản Quần Áo, Chăn Gối Nhiều Kích Cỡ – Tiết Kiệm Không Gian K152</t>
   </si>
   <si>
+    <t>290753704201</t>
+  </si>
+  <si>
+    <t>1 Túi 50CM x70CM</t>
+  </si>
+  <si>
+    <t>1TUI5070</t>
+  </si>
+  <si>
+    <t>49000</t>
+  </si>
+  <si>
+    <t>339</t>
+  </si>
+  <si>
+    <t>290753704202</t>
+  </si>
+  <si>
+    <t>1 Túi 60CM x80CM</t>
+  </si>
+  <si>
+    <t>1TUI6080</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
     <t>290753704203</t>
   </si>
   <si>
@@ -2296,34 +2320,7 @@
     <t>1TUI4060</t>
   </si>
   <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>290753704201</t>
-  </si>
-  <si>
-    <t>1 Túi 50CM x70CM</t>
-  </si>
-  <si>
-    <t>1TUI5070</t>
-  </si>
-  <si>
-    <t>49000</t>
-  </si>
-  <si>
-    <t>339</t>
-  </si>
-  <si>
-    <t>290753704202</t>
-  </si>
-  <si>
-    <t>1 Túi 60CM x80CM</t>
-  </si>
-  <si>
-    <t>1TUI6080</t>
-  </si>
-  <si>
-    <t>381</t>
+    <t>341</t>
   </si>
   <si>
     <t>29422270738</t>
@@ -2341,7 +2338,7 @@
     <t>K259_PHICHCAM90DO</t>
   </si>
   <si>
-    <t>1054</t>
+    <t>1034</t>
   </si>
   <si>
     <t>42659011561</t>
@@ -2461,7 +2458,7 @@
     <t>98000</t>
   </si>
   <si>
-    <t>288</t>
+    <t>286</t>
   </si>
   <si>
     <t>15923802936</t>
@@ -2482,9 +2479,6 @@
     <t>Đầu Vạn Năng CAO CẤP K50</t>
   </si>
   <si>
-    <t>739</t>
-  </si>
-  <si>
     <t>7617209604</t>
   </si>
   <si>
@@ -2518,12 +2512,51 @@
     <t>1 MÁY HÚT XANH</t>
   </si>
   <si>
+    <t>13840948033</t>
+  </si>
+  <si>
+    <t>Khung Lọc Rác Dính Nano K98 – Dán Gọn Thành Bồn, Ngăn Rác Hiệu Quả, Dễ Gắn Túi Lưới</t>
+  </si>
+  <si>
+    <t>168794175564</t>
+  </si>
+  <si>
+    <t>Khung Xám + 50 TÚI</t>
+  </si>
+  <si>
+    <t>KHUNGXAM50TUIK98</t>
+  </si>
+  <si>
+    <t>168794175565</t>
+  </si>
+  <si>
+    <t>Khung Xanh + 50 TÚI</t>
+  </si>
+  <si>
+    <t>khung_xanh_50_tui K98</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>8088637510</t>
   </si>
   <si>
     <t>Đầu Vòi Rửa Bát Tăng Áp K50 – Xoay 360 Độ, Lọc Nước, Lắp Siêu Dễ</t>
   </si>
   <si>
+    <t>250592592958</t>
+  </si>
+  <si>
+    <t>Đầu Vòi K50+Vạn Năng</t>
+  </si>
+  <si>
+    <t>162495_combo_dau_voi_dai_k50_dau_van_nang</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
     <t>89108481781</t>
   </si>
   <si>
@@ -2533,45 +2566,6 @@
     <t>ĐẦU VÒI LỌC NƯỚC k50</t>
   </si>
   <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>250592592958</t>
-  </si>
-  <si>
-    <t>Đầu Vòi K50+Vạn Năng</t>
-  </si>
-  <si>
-    <t>162495_combo_dau_voi_dai_k50_dau_van_nang</t>
-  </si>
-  <si>
-    <t>13840948033</t>
-  </si>
-  <si>
-    <t>Khung Lọc Rác Dính Nano K98 – Dán Gọn Thành Bồn, Ngăn Rác Hiệu Quả, Dễ Gắn Túi Lưới</t>
-  </si>
-  <si>
-    <t>168794175565</t>
-  </si>
-  <si>
-    <t>Khung Xanh + 50 TÚI</t>
-  </si>
-  <si>
-    <t>khung_xanh_50_tui K98</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>168794175564</t>
-  </si>
-  <si>
-    <t>Khung Xám + 50 TÚI</t>
-  </si>
-  <si>
-    <t>KHUNGXAM50TUIK98</t>
-  </si>
-  <si>
     <t>12460878593</t>
   </si>
   <si>
@@ -2587,7 +2581,7 @@
     <t>COMBO2LOILOCK195</t>
   </si>
   <si>
-    <t>181</t>
+    <t>179</t>
   </si>
   <si>
     <t>13415381673</t>
@@ -2605,12 +2599,27 @@
     <t>DAYVOISENTOTK231</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>19224932441</t>
   </si>
   <si>
     <t>Đầu Vòi Tăng Áp 360 Độ K189 – Lắp Cho Bồn Rửa Bát, Lavabo, Có Bộ Lọc Nước</t>
   </si>
   <si>
+    <t>201294773423</t>
+  </si>
+  <si>
+    <t>ĐầuLọc K189+Vạn Năng</t>
+  </si>
+  <si>
+    <t>297102_dauvoi_k189_van_nang</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
     <t>237384544926</t>
   </si>
   <si>
@@ -2620,18 +2629,6 @@
     <t>ĐẦU VÒI LỌC NƯỚC k189</t>
   </si>
   <si>
-    <t>170</t>
-  </si>
-  <si>
-    <t>201294773423</t>
-  </si>
-  <si>
-    <t>ĐầuLọc K189+Vạn Năng</t>
-  </si>
-  <si>
-    <t>297102_dauvoi_k189_van_nang</t>
-  </si>
-  <si>
     <t>8623440584</t>
   </si>
   <si>
@@ -2647,7 +2644,7 @@
     <t>COMBO 5 LÕI LỌCK50</t>
   </si>
   <si>
-    <t>652</t>
+    <t>651</t>
   </si>
   <si>
     <t>26958202887</t>
@@ -4071,7 +4068,7 @@
         <v>57</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="5" t="s">
@@ -4097,7 +4094,7 @@
         <v>61</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="5" t="s">
@@ -4123,7 +4120,7 @@
         <v>65</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="5" t="s">
@@ -4205,7 +4202,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="5" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="J16" s="6"/>
     </row>
@@ -4217,21 +4214,21 @@
         <v>74</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="5" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -4335,7 +4332,7 @@
         <v>109</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="5" t="s">
@@ -4361,7 +4358,7 @@
         <v>113</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="5" t="s">
@@ -4393,7 +4390,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="5" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J23" s="6"/>
     </row>
@@ -4405,21 +4402,21 @@
         <v>116</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J24" s="6"/>
     </row>
@@ -4431,21 +4428,21 @@
         <v>116</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="5" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="J25" s="6"/>
     </row>
@@ -4543,11 +4540,11 @@
         <v>150</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J29" s="6"/>
     </row>
@@ -4559,199 +4556,199 @@
         <v>142</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>155</v>
+        <v>98</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="5" t="s">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="J30" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="31">
       <c r="A31" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="5" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="J31" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="32">
       <c r="A32" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="E32" s="11"/>
+      <c r="F32" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="G32" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="5" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="J32" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="33">
       <c r="A33" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J33" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="34">
       <c r="A34" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J34" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="35">
       <c r="A35" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J35" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="36">
       <c r="A36" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="5" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="J36" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="37">
       <c r="A37" s="1" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E37" s="11"/>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="4" t="s">
         <v>189</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>177</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="5" t="s">
@@ -4777,11 +4774,11 @@
         <v>195</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="5" t="s">
-        <v>25</v>
+        <v>196</v>
       </c>
       <c r="J38" s="6"/>
     </row>
@@ -4793,21 +4790,21 @@
         <v>192</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="5" t="s">
-        <v>199</v>
+        <v>25</v>
       </c>
       <c r="J39" s="6"/>
     </row>
@@ -4829,83 +4826,83 @@
         <v>202</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="5" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="J40" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="41">
       <c r="A41" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J41" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="42">
       <c r="A42" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="C42" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="E42" s="11"/>
       <c r="F42" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J42" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="43">
       <c r="A43" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="5" t="s">
@@ -4915,49 +4912,49 @@
     </row>
     <row customHeight="true" ht="15" r="44">
       <c r="A44" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G44" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J44" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="45">
       <c r="A45" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="C45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G45" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="5" t="s">
@@ -4967,10 +4964,10 @@
     </row>
     <row customHeight="true" ht="15" r="46">
       <c r="A46" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>229</v>
@@ -4983,11 +4980,11 @@
         <v>231</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="5" t="s">
-        <v>151</v>
+        <v>232</v>
       </c>
       <c r="J46" s="6"/>
     </row>
@@ -5039,7 +5036,7 @@
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="5" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="J48" s="6"/>
     </row>
@@ -5067,42 +5064,42 @@
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="5" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="J49" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="50">
       <c r="A50" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="5" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="J50" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="51">
       <c r="A51" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>259</v>
@@ -5115,215 +5112,215 @@
         <v>261</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="5" t="s">
-        <v>262</v>
+        <v>25</v>
       </c>
       <c r="J51" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="52">
       <c r="A52" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C52" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="E52" s="11"/>
       <c r="F52" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J52" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="53">
       <c r="A53" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E53" s="11"/>
       <c r="F53" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="5" t="s">
-        <v>271</v>
+        <v>25</v>
       </c>
       <c r="J53" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="54">
       <c r="A54" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="5" t="s">
-        <v>275</v>
+        <v>25</v>
       </c>
       <c r="J54" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="55">
       <c r="A55" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="J55" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="56">
       <c r="A56" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C56" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="3" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="5" t="s">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="J56" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="57">
       <c r="A57" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C57" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="5" t="s">
-        <v>25</v>
+        <v>284</v>
       </c>
       <c r="J57" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="58">
       <c r="A58" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C58" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>266</v>
+        <v>86</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J58" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="59">
       <c r="A59" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="C59" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="5" t="s">
@@ -5333,36 +5330,36 @@
     </row>
     <row customHeight="true" ht="15" r="60">
       <c r="A60" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="5" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="J60" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="61">
       <c r="A61" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>298</v>
@@ -5375,7 +5372,7 @@
         <v>300</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="5" t="s">
@@ -5403,7 +5400,7 @@
         <v>307</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="5" t="s">
@@ -5429,152 +5426,152 @@
         <v>311</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="5" t="s">
-        <v>190</v>
+        <v>312</v>
       </c>
       <c r="J63" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="64">
       <c r="A64" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="5" t="s">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="J64" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="65">
       <c r="A65" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E65" s="11"/>
       <c r="F65" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="5" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J65" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="66">
       <c r="A66" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E66" s="11"/>
       <c r="F66" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" s="5" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="J66" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="67">
       <c r="A67" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J67" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="68">
       <c r="A68" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="5" t="s">
-        <v>330</v>
+        <v>103</v>
       </c>
       <c r="J68" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="69">
       <c r="A69" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>331</v>
@@ -5613,11 +5610,11 @@
         <v>338</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>168</v>
+        <v>339</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J70" s="6"/>
     </row>
@@ -5629,21 +5626,21 @@
         <v>335</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>91</v>
+        <v>344</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J71" s="6"/>
     </row>
@@ -5655,47 +5652,47 @@
         <v>335</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E72" s="11"/>
       <c r="F72" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>177</v>
+        <v>349</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J72" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="73">
       <c r="A73" s="1" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E73" s="11"/>
+        <v>354</v>
+      </c>
+      <c r="E73" s="3"/>
       <c r="F73" s="3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="J73" s="6"/>
     </row>
@@ -5707,199 +5704,197 @@
         <v>352</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D74" s="2"/>
-      <c r="E74" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F74" s="3"/>
+        <v>356</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E74" s="11"/>
+      <c r="F74" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="G74" s="4" t="s">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="5" t="s">
-        <v>262</v>
+        <v>359</v>
       </c>
       <c r="J74" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="75">
       <c r="A75" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D75" s="2"/>
-      <c r="E75" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>360</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E75" s="11"/>
+      <c r="F75" s="3" t="s">
+        <v>362</v>
+      </c>
       <c r="G75" s="4" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J75" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="76">
       <c r="A76" s="1" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E76" s="3" t="s">
         <v>365</v>
       </c>
+      <c r="E76" s="11"/>
       <c r="F76" s="3" t="s">
         <v>366</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" s="5" t="s">
-        <v>367</v>
+        <v>25</v>
       </c>
       <c r="J76" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="77">
       <c r="A77" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D77" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E77" s="11"/>
-      <c r="F77" s="3" t="s">
+      <c r="D77" s="2"/>
+      <c r="E77" s="3" t="s">
         <v>370</v>
       </c>
+      <c r="F77" s="3"/>
       <c r="G77" s="4" t="s">
-        <v>232</v>
+        <v>371</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="5" t="s">
-        <v>371</v>
+        <v>280</v>
       </c>
       <c r="J77" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="78">
       <c r="A78" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E78" s="11"/>
-      <c r="F78" s="3" t="s">
         <v>374</v>
       </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="5" t="s">
-        <v>25</v>
+        <v>167</v>
       </c>
       <c r="J78" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="79">
       <c r="A79" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H79" s="3"/>
       <c r="I79" s="5" t="s">
-        <v>275</v>
+        <v>167</v>
       </c>
       <c r="J79" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="80">
       <c r="A80" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E80" s="11"/>
+        <v>384</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>385</v>
+      </c>
       <c r="F80" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="H80" s="3"/>
       <c r="I80" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J80" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="81">
       <c r="A81" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>388</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="E81" s="11"/>
       <c r="F81" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>390</v>
+        <v>222</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" s="5" t="s">
@@ -5909,10 +5904,10 @@
     </row>
     <row customHeight="true" ht="15" r="82">
       <c r="A82" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>392</v>
@@ -5925,219 +5920,219 @@
         <v>394</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="5" t="s">
-        <v>395</v>
+        <v>25</v>
       </c>
       <c r="J82" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="83">
       <c r="A83" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C83" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>401</v>
-      </c>
       <c r="G83" s="4" t="s">
-        <v>402</v>
+        <v>39</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" s="5" t="s">
-        <v>403</v>
+        <v>276</v>
       </c>
       <c r="J83" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="84">
       <c r="A84" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="C84" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E84" s="11"/>
       <c r="F84" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>402</v>
+        <v>39</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" s="5" t="s">
-        <v>199</v>
+        <v>403</v>
       </c>
       <c r="J84" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="85">
       <c r="A85" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C85" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="E85" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E85" s="11"/>
       <c r="F85" s="3" t="s">
         <v>409</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" s="5" t="s">
-        <v>25</v>
+        <v>411</v>
       </c>
       <c r="J85" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="86">
       <c r="A86" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E86" s="11"/>
       <c r="F86" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>402</v>
+        <v>39</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="5" t="s">
-        <v>343</v>
+        <v>114</v>
       </c>
       <c r="J86" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="87">
       <c r="A87" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E87" s="3"/>
+        <v>418</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>419</v>
+      </c>
       <c r="F87" s="3" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>34</v>
+        <v>421</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="5" t="s">
-        <v>173</v>
+        <v>422</v>
       </c>
       <c r="J87" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="88">
       <c r="A88" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E88" s="11"/>
+      <c r="F88" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G88" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J88" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="89">
       <c r="A89" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E89" s="11"/>
       <c r="F89" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>71</v>
+        <v>421</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="5" t="s">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="J89" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="90">
       <c r="A90" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E90" s="11"/>
       <c r="F90" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>51</v>
+        <v>421</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="5" t="s">
@@ -6147,20 +6142,22 @@
     </row>
     <row customHeight="true" ht="15" r="91">
       <c r="A91" s="1" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E91" s="11"/>
+        <v>437</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>438</v>
+      </c>
       <c r="F91" s="3" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>51</v>
@@ -6179,147 +6176,147 @@
         <v>435</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="D92" s="2"/>
-      <c r="E92" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="F92" s="3"/>
+        <v>440</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E92" s="11"/>
+      <c r="F92" s="3" t="s">
+        <v>442</v>
+      </c>
       <c r="G92" s="4" t="s">
-        <v>161</v>
+        <v>71</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="5" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="J92" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="93">
       <c r="A93" s="1" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>443</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="E93" s="11"/>
       <c r="F93" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="5" t="s">
-        <v>445</v>
+        <v>387</v>
       </c>
       <c r="J93" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="94">
       <c r="A94" s="1" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="D94" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="E94" s="11"/>
+      <c r="F94" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3" t="s">
-        <v>450</v>
-      </c>
       <c r="G94" s="4" t="s">
-        <v>355</v>
+        <v>51</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="5" t="s">
-        <v>383</v>
+        <v>25</v>
       </c>
       <c r="J94" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="95">
       <c r="A95" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C95" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="D95" s="2"/>
+      <c r="E95" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3" t="s">
-        <v>455</v>
-      </c>
+      <c r="F95" s="3"/>
       <c r="G95" s="4" t="s">
-        <v>456</v>
+        <v>189</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J95" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="96">
       <c r="A96" s="1" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C96" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="E96" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="E96" s="11"/>
       <c r="F96" s="3" t="s">
         <v>460</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>461</v>
+        <v>222</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="J96" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="97">
       <c r="A97" s="1" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E97" s="11"/>
+        <v>465</v>
+      </c>
+      <c r="E97" s="3"/>
       <c r="F97" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>466</v>
+        <v>371</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="5" t="s">
@@ -6343,11 +6340,11 @@
       </c>
       <c r="F98" s="3"/>
       <c r="G98" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="5" t="s">
-        <v>371</v>
+        <v>110</v>
       </c>
       <c r="J98" s="6"/>
     </row>
@@ -6367,11 +6364,11 @@
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="4" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="5" t="s">
-        <v>360</v>
+        <v>284</v>
       </c>
       <c r="J99" s="6"/>
     </row>
@@ -6419,7 +6416,7 @@
         <v>487</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="5" t="s">
@@ -6447,11 +6444,11 @@
         <v>494</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="5" t="s">
-        <v>495</v>
+        <v>25</v>
       </c>
       <c r="J102" s="6"/>
     </row>
@@ -6463,202 +6460,202 @@
         <v>490</v>
       </c>
       <c r="C103" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>497</v>
       </c>
       <c r="E103" s="11"/>
       <c r="F103" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="5" t="s">
-        <v>25</v>
+        <v>172</v>
       </c>
       <c r="J103" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="104">
       <c r="A104" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="D104" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="E104" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="F104" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="G104" s="4" t="s">
         <v>139</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J104" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="105">
       <c r="A105" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C105" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="E105" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="F105" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>511</v>
-      </c>
       <c r="G105" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J105" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="106">
       <c r="A106" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C106" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="D106" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="E106" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="E106" s="3" t="s">
+      <c r="F106" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>518</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J106" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="107">
       <c r="A107" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="C107" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>520</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="E107" s="11"/>
       <c r="F107" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J107" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="108">
       <c r="A108" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="C108" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J108" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="109">
       <c r="A109" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="5" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="J109" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="110">
       <c r="A110" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C110" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="D110" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G110" s="4" t="s">
         <v>71</v>
@@ -6671,20 +6668,20 @@
     </row>
     <row customHeight="true" ht="15" r="111">
       <c r="A111" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="C111" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="E111" s="11"/>
       <c r="F111" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G111" s="4" t="s">
         <v>71</v>
@@ -6697,75 +6694,75 @@
     </row>
     <row customHeight="true" ht="15" r="112">
       <c r="A112" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="C112" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="E112" s="11"/>
       <c r="F112" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G112" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="J112" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="113">
       <c r="A113" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="G113" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>551</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="5" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J113" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="114">
       <c r="A114" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>555</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>556</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="5" t="s">
@@ -6775,251 +6772,251 @@
     </row>
     <row customHeight="true" ht="15" r="115">
       <c r="A115" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>554</v>
-      </c>
       <c r="C115" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="E115" s="11"/>
       <c r="F115" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="5" t="s">
-        <v>561</v>
+        <v>196</v>
       </c>
       <c r="J115" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="116">
       <c r="A116" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="D116" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>39</v>
+        <v>565</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="5" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J116" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="117">
       <c r="A117" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C117" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="E117" s="11"/>
       <c r="F117" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>571</v>
+        <v>44</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="5" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J117" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="118">
       <c r="A118" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="D118" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>481</v>
+        <v>339</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J118" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="119">
       <c r="A119" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E119" s="11"/>
       <c r="F119" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>481</v>
+        <v>339</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="J119" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="120">
       <c r="A120" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E120" s="11"/>
       <c r="F120" s="3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>481</v>
+        <v>339</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J120" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="121">
       <c r="A121" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E121" s="11"/>
       <c r="F121" s="3" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="H121" s="3"/>
       <c r="I121" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="J121" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="122">
       <c r="A122" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E122" s="11"/>
       <c r="F122" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="H122" s="3"/>
       <c r="I122" s="5" t="s">
-        <v>552</v>
+        <v>592</v>
       </c>
       <c r="J122" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="123">
       <c r="A123" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C123" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="E123" s="11"/>
       <c r="F123" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="H123" s="3"/>
       <c r="I123" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J123" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="124">
       <c r="A124" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="4" t="s">
@@ -7027,55 +7024,55 @@
       </c>
       <c r="H124" s="3"/>
       <c r="I124" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="J124" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="125">
       <c r="A125" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C125" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C125" s="2" t="s">
+      <c r="D125" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="G125" s="4" t="s">
         <v>606</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="H125" s="3"/>
       <c r="I125" s="5" t="s">
-        <v>607</v>
+        <v>25</v>
       </c>
       <c r="J125" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="126">
       <c r="A126" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="C126" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="E126" s="11"/>
       <c r="F126" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>611</v>
+        <v>189</v>
       </c>
       <c r="H126" s="3"/>
       <c r="I126" s="5" t="s">
@@ -7085,23 +7082,23 @@
     </row>
     <row customHeight="true" ht="15" r="127">
       <c r="A127" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="C127" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E127" s="11"/>
       <c r="F127" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>161</v>
+        <v>613</v>
       </c>
       <c r="H127" s="3"/>
       <c r="I127" s="5" t="s">
@@ -7111,519 +7108,519 @@
     </row>
     <row customHeight="true" ht="15" r="128">
       <c r="A128" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="C128" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D128" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="E128" s="11"/>
       <c r="F128" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>618</v>
+        <v>71</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="5" t="s">
-        <v>25</v>
+        <v>482</v>
       </c>
       <c r="J128" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="129">
       <c r="A129" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="C129" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E129" s="11"/>
       <c r="F129" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="H129" s="3"/>
       <c r="I129" s="5" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J129" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="130">
       <c r="A130" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>625</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H130" s="3"/>
       <c r="I130" s="5" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="J130" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="131">
       <c r="A131" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="D131" s="2" t="s">
         <v>629</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G131" s="4" t="s">
         <v>251</v>
       </c>
       <c r="H131" s="3"/>
       <c r="I131" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="J131" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="132">
       <c r="A132" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="D132" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G132" s="4" t="s">
         <v>251</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="5" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="J132" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="133">
       <c r="A133" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="D133" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H133" s="3"/>
       <c r="I133" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="J133" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="134">
       <c r="A134" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="D134" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="J134" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="135">
       <c r="A135" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="D135" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>654</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>466</v>
+        <v>86</v>
       </c>
       <c r="H135" s="3"/>
       <c r="I135" s="5" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="J135" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="136">
       <c r="A136" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E136" s="11"/>
       <c r="F136" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="H136" s="3"/>
       <c r="I136" s="5" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J136" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="137">
       <c r="A137" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C137" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="E137" s="11"/>
       <c r="F137" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>664</v>
+        <v>349</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="5" t="s">
-        <v>665</v>
+        <v>596</v>
       </c>
       <c r="J137" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="138">
       <c r="A138" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>668</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>671</v>
+        <v>34</v>
       </c>
       <c r="H138" s="3"/>
       <c r="I138" s="5" t="s">
-        <v>25</v>
+        <v>668</v>
       </c>
       <c r="J138" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="139">
       <c r="A139" s="1" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E139" s="11"/>
       <c r="F139" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>44</v>
+        <v>672</v>
       </c>
       <c r="H139" s="3"/>
       <c r="I139" s="5" t="s">
-        <v>675</v>
+        <v>25</v>
       </c>
       <c r="J139" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="140">
       <c r="A140" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H140" s="3"/>
       <c r="I140" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J140" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="141">
       <c r="A141" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="D141" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>683</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>684</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H141" s="3"/>
       <c r="I141" s="5" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="J141" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="142">
       <c r="A142" s="1" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H142" s="3"/>
       <c r="I142" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J142" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="143">
       <c r="A143" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H143" s="3"/>
       <c r="I143" s="5" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="J143" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="144">
       <c r="A144" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H144" s="3"/>
       <c r="I144" s="5" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="J144" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="145">
       <c r="A145" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E145" s="11"/>
       <c r="F145" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H145" s="3"/>
       <c r="I145" s="5" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="J145" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="146">
       <c r="A146" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E146" s="11"/>
       <c r="F146" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H146" s="3"/>
       <c r="I146" s="5" t="s">
-        <v>523</v>
+        <v>706</v>
       </c>
       <c r="J146" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="147">
       <c r="A147" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="D147" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>711</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H147" s="3"/>
       <c r="I147" s="5" t="s">
-        <v>203</v>
+        <v>712</v>
       </c>
       <c r="J147" s="6"/>
     </row>
@@ -7645,7 +7642,7 @@
         <v>717</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H148" s="3"/>
       <c r="I148" s="5" t="s">
@@ -7671,11 +7668,11 @@
         <v>723</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="H149" s="3"/>
       <c r="I149" s="5" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="J149" s="6"/>
     </row>
@@ -7701,7 +7698,7 @@
       </c>
       <c r="H150" s="3"/>
       <c r="I150" s="5" t="s">
-        <v>728</v>
+        <v>584</v>
       </c>
       <c r="J150" s="6"/>
     </row>
@@ -7713,17 +7710,17 @@
         <v>720</v>
       </c>
       <c r="C151" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="D151" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>730</v>
       </c>
       <c r="E151" s="11"/>
       <c r="F151" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="G151" s="4" t="s">
         <v>731</v>
-      </c>
-      <c r="G151" s="4" t="s">
-        <v>732</v>
       </c>
       <c r="H151" s="3"/>
       <c r="I151" s="5" t="s">
@@ -7733,179 +7730,179 @@
     </row>
     <row customHeight="true" ht="15" r="152">
       <c r="A152" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="H152" s="3"/>
       <c r="I152" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J152" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="153">
       <c r="A153" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>734</v>
-      </c>
       <c r="C153" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>739</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>740</v>
       </c>
       <c r="E153" s="11"/>
       <c r="F153" s="3" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>466</v>
+        <v>349</v>
       </c>
       <c r="H153" s="3"/>
       <c r="I153" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J153" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="154">
       <c r="A154" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>734</v>
-      </c>
       <c r="C154" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="E154" s="11"/>
       <c r="F154" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H154" s="3"/>
       <c r="I154" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="J154" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="155">
       <c r="A155" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="C155" s="2" t="s">
-        <v>748</v>
-      </c>
       <c r="D155" s="2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="H155" s="3"/>
       <c r="I155" s="5" t="s">
-        <v>660</v>
+        <v>596</v>
       </c>
       <c r="J155" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="156">
       <c r="A156" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>747</v>
-      </c>
       <c r="C156" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="E156" s="11"/>
       <c r="F156" s="3" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>664</v>
+        <v>86</v>
       </c>
       <c r="H156" s="3"/>
       <c r="I156" s="5" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="J156" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="157">
       <c r="A157" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>747</v>
-      </c>
       <c r="C157" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E157" s="11"/>
       <c r="F157" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>466</v>
+        <v>658</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="J157" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="158">
       <c r="A158" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C158" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="D158" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="G158" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="G158" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="H158" s="3"/>
       <c r="I158" s="5" t="s">
@@ -7915,10 +7912,10 @@
     </row>
     <row customHeight="true" ht="15" r="159">
       <c r="A159" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>757</v>
@@ -7931,7 +7928,7 @@
         <v>759</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="H159" s="3"/>
       <c r="I159" s="5" t="s">
@@ -7941,10 +7938,10 @@
     </row>
     <row customHeight="true" ht="15" r="160">
       <c r="A160" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>752</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>761</v>
@@ -7957,191 +7954,191 @@
         <v>763</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>764</v>
+        <v>39</v>
       </c>
       <c r="H160" s="3"/>
       <c r="I160" s="5" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="J160" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="161">
       <c r="A161" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>752</v>
-      </c>
       <c r="C161" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="D161" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="E161" s="11"/>
       <c r="F161" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="H161" s="3"/>
       <c r="I161" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="J161" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="162">
       <c r="A162" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="C162" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="D162" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>161</v>
+        <v>189</v>
       </c>
       <c r="H162" s="3"/>
       <c r="I162" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="J162" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="163">
       <c r="A163" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="D163" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="H163" s="3"/>
       <c r="I163" s="5" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="J163" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="164">
       <c r="A164" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="C164" s="2" t="s">
+      <c r="D164" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>784</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>456</v>
+        <v>339</v>
       </c>
       <c r="H164" s="3"/>
       <c r="I164" s="5" t="s">
-        <v>62</v>
+        <v>297</v>
       </c>
       <c r="J164" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="165">
       <c r="A165" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="C165" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="D165" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="G165" s="4" t="s">
         <v>790</v>
-      </c>
-      <c r="G165" s="4" t="s">
-        <v>791</v>
       </c>
       <c r="H165" s="3"/>
       <c r="I165" s="5" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="J165" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="166">
       <c r="A166" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="C166" s="2" t="s">
         <v>794</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="E166" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="E166" s="3" t="s">
+      <c r="F166" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="F166" s="3" t="s">
-        <v>798</v>
-      </c>
       <c r="G166" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H166" s="3"/>
       <c r="I166" s="5" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J166" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="167">
       <c r="A167" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>794</v>
-      </c>
       <c r="C167" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="E167" s="11"/>
       <c r="F167" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H167" s="3"/>
       <c r="I167" s="5" t="s">
@@ -8151,20 +8148,20 @@
     </row>
     <row customHeight="true" ht="15" r="168">
       <c r="A168" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>794</v>
-      </c>
       <c r="C168" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="D168" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>804</v>
       </c>
       <c r="E168" s="11"/>
       <c r="F168" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G168" s="4" t="s">
         <v>71</v>
@@ -8177,395 +8174,395 @@
     </row>
     <row customHeight="true" ht="15" r="169">
       <c r="A169" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>793</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>794</v>
-      </c>
       <c r="C169" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="D169" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="E169" s="11"/>
       <c r="F169" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H169" s="3"/>
       <c r="I169" s="5" t="s">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="J169" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="170">
       <c r="A170" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="C170" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="D170" s="2" t="s">
         <v>811</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>812</v>
       </c>
       <c r="E170" s="3"/>
       <c r="F170" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="G170" s="4" t="s">
         <v>813</v>
-      </c>
-      <c r="G170" s="4" t="s">
-        <v>814</v>
       </c>
       <c r="H170" s="3"/>
       <c r="I170" s="5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="J170" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="171">
       <c r="A171" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="C171" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="C171" s="2" t="s">
+      <c r="D171" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="D171" s="2" t="s">
+      <c r="E171" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="E171" s="3" t="s">
+      <c r="F171" s="3" t="s">
         <v>820</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>821</v>
       </c>
       <c r="G171" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H171" s="3"/>
       <c r="I171" s="5" t="s">
-        <v>822</v>
+        <v>488</v>
       </c>
       <c r="J171" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="172">
       <c r="A172" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="D172" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="C172" s="2" t="s">
+      <c r="E172" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="D172" s="2" t="s">
+      <c r="F172" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="E172" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>828</v>
-      </c>
       <c r="G172" s="4" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="H172" s="3"/>
       <c r="I172" s="5" t="s">
-        <v>495</v>
+        <v>172</v>
       </c>
       <c r="J172" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="173">
       <c r="A173" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="D173" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>832</v>
       </c>
       <c r="E173" s="3"/>
       <c r="F173" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H173" s="3"/>
       <c r="I173" s="5" t="s">
-        <v>238</v>
+        <v>133</v>
       </c>
       <c r="J173" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="174">
       <c r="A174" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="D174" s="2" t="s">
         <v>835</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>837</v>
       </c>
       <c r="E174" s="3"/>
       <c r="F174" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="H174" s="3"/>
       <c r="I174" s="5" t="s">
-        <v>839</v>
+        <v>461</v>
       </c>
       <c r="J174" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="175">
       <c r="A175" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E175" s="11"/>
       <c r="F175" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="H175" s="3"/>
       <c r="I175" s="5" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="J175" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="176">
       <c r="A176" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="D176" s="2" t="s">
         <v>844</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>846</v>
       </c>
       <c r="E176" s="3"/>
       <c r="F176" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="H176" s="3"/>
       <c r="I176" s="5" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="J176" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="177">
       <c r="A177" s="1" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E177" s="11"/>
       <c r="F177" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="H177" s="3"/>
       <c r="I177" s="5" t="s">
-        <v>445</v>
+        <v>846</v>
       </c>
       <c r="J177" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="178">
       <c r="A178" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="D178" s="2" t="s">
         <v>853</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>855</v>
       </c>
       <c r="E178" s="3"/>
       <c r="F178" s="3" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H178" s="3"/>
       <c r="I178" s="5" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="J178" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="179">
       <c r="A179" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="D179" s="2" t="s">
         <v>859</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>861</v>
       </c>
       <c r="E179" s="3"/>
       <c r="F179" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H179" s="3"/>
       <c r="I179" s="5" t="s">
-        <v>262</v>
+        <v>861</v>
       </c>
       <c r="J179" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="180">
       <c r="A180" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="C180" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="C180" s="2" t="s">
+      <c r="D180" s="2" t="s">
         <v>865</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>866</v>
       </c>
       <c r="E180" s="3"/>
       <c r="F180" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>232</v>
+        <v>39</v>
       </c>
       <c r="H180" s="3"/>
       <c r="I180" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J180" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="181">
       <c r="A181" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>864</v>
-      </c>
       <c r="C181" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D181" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>870</v>
       </c>
       <c r="E181" s="11"/>
       <c r="F181" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="H181" s="3"/>
       <c r="I181" s="5" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J181" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="182">
       <c r="A182" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="C182" s="2" t="s">
         <v>873</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="D182" s="2" t="s">
         <v>874</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>875</v>
       </c>
       <c r="E182" s="3"/>
       <c r="F182" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H182" s="3"/>
       <c r="I182" s="5" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="J182" s="6"/>
     </row>
     <row customHeight="true" ht="15" r="183">
       <c r="A183" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B183" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="C183" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="D183" s="2" t="s">
         <v>880</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>881</v>
       </c>
       <c r="E183" s="3"/>
       <c r="F183" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H183" s="3"/>
       <c r="I183" s="5" t="s">
-        <v>262</v>
+        <v>861</v>
       </c>
       <c r="J183" s="6"/>
     </row>
